--- a/Materials/Расписание 2026-2027/Расписание_V34_для_завуча_цветное.xlsx
+++ b/Materials/Расписание 2026-2027/Расписание_V34_для_завуча_цветное.xlsx
@@ -140,7 +140,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B6D7E1"/>
+        <fgColor rgb="00CCEAD7"/>
       </patternFill>
     </fill>
     <fill>
@@ -175,7 +175,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00C7D0EE"/>
+        <fgColor rgb="00EEC7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -185,7 +185,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CFCCEA"/>
+        <fgColor rgb="00B6D7E1"/>
       </patternFill>
     </fill>
     <fill>
@@ -210,7 +210,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8B3AF"/>
+        <fgColor rgb="00B9E8AF"/>
       </patternFill>
     </fill>
     <fill>
@@ -385,12 +385,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00B9E8AF"/>
+        <fgColor rgb="00EEECC7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00CCEAD7"/>
+        <fgColor rgb="00CFCCEA"/>
       </patternFill>
     </fill>
     <fill>
@@ -410,7 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEC7DA"/>
+        <fgColor rgb="00D4AFE8"/>
       </patternFill>
     </fill>
     <fill>
@@ -520,7 +520,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EEECC7"/>
+        <fgColor rgb="00E8B3AF"/>
       </patternFill>
     </fill>
     <fill>
@@ -559,16 +559,6 @@
       </patternFill>
     </fill>
     <fill>
-      <gradientFill type="linear">
-        <stop position="0">
-          <color rgb="00B6B7E1"/>
-        </stop>
-        <stop position="1">
-          <color rgb="00AFE8E2"/>
-        </stop>
-      </gradientFill>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00AFDFE8"/>
       </patternFill>
@@ -596,6 +586,16 @@
     <fill>
       <gradientFill type="linear">
         <stop position="0">
+          <color rgb="00B6B7E1"/>
+        </stop>
+        <stop position="1">
+          <color rgb="00AFE8E2"/>
+        </stop>
+      </gradientFill>
+    </fill>
+    <fill>
+      <gradientFill type="linear">
+        <stop position="0">
           <color rgb="00AFE8DE"/>
         </stop>
         <stop position="1">
@@ -605,7 +605,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4AFE8"/>
+        <fgColor rgb="00C7D0EE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1085,10 +1085,10 @@
     <xf numFmtId="0" fontId="3" fillId="95" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="96" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="96" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="97" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="97" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="98" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1133,7 +1133,7 @@
     <xf numFmtId="0" fontId="3" fillId="111" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="94" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="99" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="112" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1192,250 +1192,250 @@
     <xf numFmtId="0" fontId="3" fillId="115" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="94" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="113" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="50" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="108" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="105" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="56" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="70" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="87" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="48" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="69" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="77" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="71" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="116" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="42" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="84" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="103" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="85" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="57" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="111" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="61" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="60" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="65" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="86" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="101" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="104" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="90" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="96" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="74" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="63" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="49" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="58" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="114" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="112" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="88" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="117" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="106" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="72" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="75" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="62" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="98" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="55" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="78" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="51" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="79" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="80" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="110" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="73" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="53" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="95" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="113" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="50" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="108" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="105" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="56" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="70" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="37" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="87" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="48" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="69" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="77" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="71" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="116" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="45" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="42" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="36" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="44" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="84" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="103" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="85" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="57" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="111" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="60" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="65" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="86" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="101" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="61" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="104" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="90" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="97" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="74" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="63" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="49" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="58" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="114" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="112" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="88" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="117" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="34" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="41" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="106" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="72" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="75" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="38" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="62" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="99" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="55" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="78" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="51" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="79" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="35" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="80" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="110" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="73" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="53" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="96" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="46" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="98" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="97" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="93" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1490,10 +1490,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="118" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="119" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="118" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -2134,7 +2134,7 @@
       <c r="R3" s="21" t="inlineStr">
         <is>
           <t>КиЛ
-Дюсембаева А.К., каб. английского языка (№27)</t>
+Власова А.К., каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="S3" s="22" t="inlineStr">
@@ -2188,7 +2188,7 @@
       <c r="F4" s="29" t="inlineStr">
         <is>
           <t>Казахский язык
-Дюсембаева А.К., нач. класс 1Б (№8)</t>
+Власова А.К., нач. класс 1Б (№8)</t>
         </is>
       </c>
       <c r="G4" s="30" t="inlineStr">
@@ -2335,7 +2335,7 @@
       <c r="H5" s="29" t="inlineStr">
         <is>
           <t>Казахский язык
-Дюсембаева А.К., нач. класс 3А (№7)</t>
+Власова А.К., нач. класс 3А (№7)</t>
         </is>
       </c>
       <c r="I5" s="45" t="inlineStr">
@@ -2377,14 +2377,14 @@
       <c r="O5" s="50" t="inlineStr">
         <is>
           <t>Русский язык
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. математики (№25)
 вместе с 6В</t>
         </is>
       </c>
       <c r="P5" s="50" t="inlineStr">
         <is>
           <t>Русский язык
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. математики (№25)
 вместе с 6Б</t>
         </is>
       </c>
@@ -2506,7 +2506,7 @@
       <c r="N6" s="60" t="inlineStr">
         <is>
           <t>Русская лит.
-Ажикенова М.А., каб. робототехники (№15)</t>
+Ажикенова М.А., каб. мультимедийный (№18)</t>
         </is>
       </c>
       <c r="O6" s="61" t="inlineStr">
@@ -2681,7 +2681,7 @@
       <c r="L8" s="67" t="inlineStr">
         <is>
           <t>Каз. литература
-Дюсембаева А.К., каб. НВП (№28)</t>
+Власова А.К., каб. НВП (№28)</t>
         </is>
       </c>
       <c r="M8" s="47" t="inlineStr">
@@ -3034,7 +3034,7 @@
       <c r="Q12" s="21" t="inlineStr">
         <is>
           <t>КиЛ
-Дюсембаева А.К., каб. физики (№16)</t>
+Власова А.К., каб. физики (№16)</t>
         </is>
       </c>
       <c r="R12" s="62" t="inlineStr">
@@ -3137,7 +3137,7 @@
       <c r="L13" s="29" t="inlineStr">
         <is>
           <t>Казахский язык
-Дюсембаева А.К., каб. физики (№16)</t>
+Власова А.К., каб. физики (№16)</t>
         </is>
       </c>
       <c r="M13" s="85" t="inlineStr">
@@ -3307,7 +3307,7 @@
       <c r="R14" s="21" t="inlineStr">
         <is>
           <t>КиЛ
-Дюсембаева А.К., каб. физики (№16)</t>
+Власова А.К., каб. физики (№16)</t>
         </is>
       </c>
       <c r="S14" s="77" t="inlineStr">
@@ -3395,14 +3395,14 @@
       <c r="O15" s="93" t="inlineStr">
         <is>
           <t>Русская лит.
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. английского языка (№27)
 вместе с 6В</t>
         </is>
       </c>
       <c r="P15" s="94" t="inlineStr">
         <is>
           <t>Чтение и разв. речи
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. английского языка (№27)
 вместе с 6Б</t>
         </is>
       </c>
@@ -3965,14 +3965,14 @@
       <c r="O21" s="50" t="inlineStr">
         <is>
           <t>Русский язык
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. биологии (№19)
 вместе с 6В</t>
         </is>
       </c>
       <c r="P21" s="50" t="inlineStr">
         <is>
           <t>Русский язык
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. биологии (№19)
 вместе с 6Б</t>
         </is>
       </c>
@@ -3985,7 +3985,7 @@
       <c r="R21" s="21" t="inlineStr">
         <is>
           <t>КиЛ
-Дюсембаева А.К., каб. английского языка (№27)</t>
+Власова А.К., каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="S21" s="40" t="inlineStr">
@@ -4036,7 +4036,7 @@
       <c r="D22" s="64" t="inlineStr">
         <is>
           <t>Казахский язык
-Жекеева Н.А., каб. технологии (девочки) (№29)</t>
+Жекеева Н.А., нач. класс 2А/4А (№42)</t>
         </is>
       </c>
       <c r="E22" s="56" t="inlineStr">
@@ -4108,12 +4108,10 @@
         </is>
       </c>
       <c r="P22" s="23" t="n"/>
-      <c r="Q22" s="106" t="inlineStr">
-        <is>
-          <t>Девочки: Худ.труд
-Жукова И.М., каб. технологии (девочки) (№29)
-Мальчики: Худ.труд
-Жантимиров А.К., каб. технологии (мальчики) (№39)</t>
+      <c r="Q22" s="57" t="inlineStr">
+        <is>
+          <t>Физкультура
+Ольков Г.В., спортзал (№01)</t>
         </is>
       </c>
       <c r="R22" s="52" t="inlineStr">
@@ -4167,40 +4165,40 @@
 Ольков Г.В., спортзал (№01)</t>
         </is>
       </c>
-      <c r="H23" s="107" t="inlineStr">
+      <c r="H23" s="106" t="inlineStr">
         <is>
           <t>Англ.язык
 Акауова И.Н., нач. класс 3А (№7)</t>
         </is>
       </c>
-      <c r="I23" s="108" t="inlineStr">
+      <c r="I23" s="107" t="inlineStr">
         <is>
           <t>Труд. обучение
 Радионова Н.А., каб. технологии (девочки) (№29)</t>
         </is>
       </c>
-      <c r="J23" s="109" t="inlineStr">
+      <c r="J23" s="108" t="inlineStr">
         <is>
           <t>Худ.труд
 Жантимиров А.К., каб. технологии (мальчики) (№39)
 вместе с 6А, 8Ә</t>
         </is>
       </c>
-      <c r="K23" s="109" t="inlineStr">
+      <c r="K23" s="108" t="inlineStr">
         <is>
           <t>Худ.труд
 Жантимиров А.К., каб. технологии (мальчики) (№39)
 вместе с 5А, 8Ә</t>
         </is>
       </c>
-      <c r="L23" s="109" t="inlineStr">
+      <c r="L23" s="108" t="inlineStr">
         <is>
           <t>Худ.труд
 Жантимиров А.К., каб. технологии (мальчики) (№39)
 вместе с 5А, 6А</t>
         </is>
       </c>
-      <c r="M23" s="110" t="inlineStr">
+      <c r="M23" s="109" t="inlineStr">
         <is>
           <t>География
 Сапаргалиева Г.С., каб. математики (№25)</t>
@@ -4212,7 +4210,7 @@
 Бучкова И.О., каб. робототехники (№15)</t>
         </is>
       </c>
-      <c r="O23" s="111" t="inlineStr">
+      <c r="O23" s="110" t="inlineStr">
         <is>
           <t>Всем.история
 Мельникова Л.Р., каб. истории (№14)</t>
@@ -4222,7 +4220,7 @@
       <c r="Q23" s="21" t="inlineStr">
         <is>
           <t>КиЛ
-Дюсембаева А.К., каб. английского языка (№27)</t>
+Власова А.К., каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="R23" s="39" t="inlineStr">
@@ -4290,7 +4288,7 @@
       <c r="L24" s="67" t="inlineStr">
         <is>
           <t>Каз. литература
-Дюсембаева А.К., каб. английского языка (№27)</t>
+Власова А.К., каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="M24" s="35" t="inlineStr">
@@ -4300,7 +4298,7 @@
         </is>
       </c>
       <c r="N24" s="23" t="n"/>
-      <c r="O24" s="106" t="inlineStr">
+      <c r="O24" s="111" t="inlineStr">
         <is>
           <t>Девочки: Худ.труд
 Жукова И.М., каб. технологии (девочки) (№29)
@@ -4309,10 +4307,10 @@
         </is>
       </c>
       <c r="P24" s="23" t="n"/>
-      <c r="Q24" s="57" t="inlineStr">
-        <is>
-          <t>Физкультура
-Ольков Г.В., спортзал (№01)</t>
+      <c r="Q24" s="52" t="inlineStr">
+        <is>
+          <t>Физика
+Русина Н.В., каб. физики (№16)</t>
         </is>
       </c>
       <c r="R24" s="97" t="inlineStr">
@@ -4362,7 +4360,7 @@
       <c r="I25" s="23" t="n"/>
       <c r="J25" s="23" t="n"/>
       <c r="K25" s="23" t="n"/>
-      <c r="L25" s="110" t="inlineStr">
+      <c r="L25" s="109" t="inlineStr">
         <is>
           <t>География
 Сапаргалиева Г.С., каб. математики (№25)</t>
@@ -4372,12 +4370,7 @@
       <c r="N25" s="23" t="n"/>
       <c r="O25" s="23" t="n"/>
       <c r="P25" s="23" t="n"/>
-      <c r="Q25" s="52" t="inlineStr">
-        <is>
-          <t>Физика
-Русина Н.В., каб. физики (№16)</t>
-        </is>
-      </c>
+      <c r="Q25" s="23" t="n"/>
       <c r="R25" s="23" t="n"/>
       <c r="S25" s="57" t="inlineStr">
         <is>
@@ -4495,7 +4488,7 @@
       <c r="L27" s="29" t="inlineStr">
         <is>
           <t>Казахский язык
-Дюсембаева А.К., каб. НВП (№28)</t>
+Власова А.К., каб. НВП (№28)</t>
         </is>
       </c>
       <c r="M27" s="33" t="inlineStr">
@@ -4657,7 +4650,7 @@
       <c r="Q28" s="21" t="inlineStr">
         <is>
           <t>КиЛ
-Дюсембаева А.К., каб. НВП (№28)</t>
+Власова А.К., каб. НВП (№28)</t>
         </is>
       </c>
       <c r="R28" s="42" t="inlineStr">
@@ -4724,7 +4717,7 @@
       <c r="F29" s="29" t="inlineStr">
         <is>
           <t>Казахский язык
-Дюсембаева А.К., нач. класс 1Б (№8)</t>
+Власова А.К., нач. класс 1Б (№8)</t>
         </is>
       </c>
       <c r="G29" s="118" t="inlineStr">
@@ -4864,7 +4857,7 @@
       <c r="H30" s="29" t="inlineStr">
         <is>
           <t>Казахский язык
-Дюсембаева А.К., нач. класс 3А (№7)</t>
+Власова А.К., нач. класс 3А (№7)</t>
         </is>
       </c>
       <c r="I30" s="33" t="inlineStr">
@@ -4906,14 +4899,14 @@
       <c r="O30" s="93" t="inlineStr">
         <is>
           <t>Русская лит.
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. истории (№14)
 вместе с 6В</t>
         </is>
       </c>
       <c r="P30" s="94" t="inlineStr">
         <is>
           <t>Чтение и разв. речи
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. истории (№14)
 вместе с 6Б</t>
         </is>
       </c>
@@ -4993,10 +4986,10 @@
 Балгабаева Н.К., каб. казахского языка и литературы (№23)</t>
         </is>
       </c>
-      <c r="L31" s="75" t="inlineStr">
-        <is>
-          <t>Геометрия
-Ізбасты М.Ж., каб. робототехники (№15)</t>
+      <c r="L31" s="74" t="inlineStr">
+        <is>
+          <t>Всем.история
+Досаева М.Х., каб. истории (№14)</t>
         </is>
       </c>
       <c r="M31" s="88" t="inlineStr">
@@ -5005,7 +4998,7 @@
 Байгазиева А.Д., каб. биологии (№19)</t>
         </is>
       </c>
-      <c r="N31" s="106" t="inlineStr">
+      <c r="N31" s="111" t="inlineStr">
         <is>
           <t>Девочки: Худ.труд
 Жукова И.М., каб. технологии (девочки) (№29)
@@ -5016,7 +5009,7 @@
       <c r="O31" s="61" t="inlineStr">
         <is>
           <t>История Каз.
-Мельникова Л.Р., каб. истории (№14)</t>
+Мельникова Л.Р., каб. робототехники (№15)</t>
         </is>
       </c>
       <c r="P31" s="23" t="n"/>
@@ -5029,7 +5022,7 @@
       <c r="R31" s="21" t="inlineStr">
         <is>
           <t>КиЛ
-Дюсембаева А.К., каб. английского языка (№27)</t>
+Власова А.К., каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="S31" s="77" t="inlineStr">
@@ -5078,13 +5071,13 @@
         </is>
       </c>
       <c r="K32" s="23" t="n"/>
-      <c r="L32" s="74" t="inlineStr">
-        <is>
-          <t>Всем.история
-Досаева М.Х., каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="M32" s="110" t="inlineStr">
+      <c r="L32" s="75" t="inlineStr">
+        <is>
+          <t>Геометрия
+Ізбасты М.Ж., каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="M32" s="109" t="inlineStr">
         <is>
           <t>География
 Сапаргалиева Г.С., каб. математики (№25)</t>
@@ -5156,7 +5149,7 @@
       <c r="I33" s="23" t="n"/>
       <c r="J33" s="23" t="n"/>
       <c r="K33" s="23" t="n"/>
-      <c r="L33" s="110" t="inlineStr">
+      <c r="L33" s="109" t="inlineStr">
         <is>
           <t>География
 Сапаргалиева Г.С., каб. математики (№25)</t>
@@ -5177,7 +5170,7 @@
 Ольков Г.В., спортзал (№01)</t>
         </is>
       </c>
-      <c r="R33" s="106" t="inlineStr">
+      <c r="R33" s="111" t="inlineStr">
         <is>
           <t>Девочки: Худ.труд
 Жукова И.М., каб. технологии (девочки) (№29)
@@ -5298,10 +5291,10 @@
 Ізбасты М.Ж., каб. НВП (№28)</t>
         </is>
       </c>
-      <c r="L35" s="67" t="inlineStr">
-        <is>
-          <t>Каз. литература
-Дюсембаева А.К., каб. английского языка (№27)</t>
+      <c r="L35" s="29" t="inlineStr">
+        <is>
+          <t>Казахский язык
+Власова А.К., каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="M35" s="98" t="inlineStr">
@@ -5330,10 +5323,12 @@
 вместе с 6Б</t>
         </is>
       </c>
-      <c r="Q35" s="52" t="inlineStr">
-        <is>
-          <t>Физика
-Русина Н.В., каб. физики (№16)</t>
+      <c r="Q35" s="111" t="inlineStr">
+        <is>
+          <t>Девочки: Худ.труд
+Жукова И.М., каб. технологии (девочки) (№29)
+Мальчики: Худ.труд
+Жантимиров А.К., каб. технологии (мальчики) (№39)</t>
         </is>
       </c>
       <c r="R35" s="24" t="inlineStr">
@@ -5463,7 +5458,7 @@
       <c r="Q36" s="21" t="inlineStr">
         <is>
           <t>КиЛ
-Дюсембаева А.К., каб. английского языка (№27)</t>
+Власова А.К., каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="R36" s="22" t="inlineStr">
@@ -5551,14 +5546,14 @@
 Асаева Ж.Х., нач. класс 4Б (№9)</t>
         </is>
       </c>
-      <c r="J37" s="109" t="inlineStr">
+      <c r="J37" s="108" t="inlineStr">
         <is>
           <t>Худ.труд
 Жантимиров А.К., каб. технологии (мальчики) (№39)
 вместе с 6А</t>
         </is>
       </c>
-      <c r="K37" s="109" t="inlineStr">
+      <c r="K37" s="108" t="inlineStr">
         <is>
           <t>Худ.труд
 Жантимиров А.К., каб. технологии (мальчики) (№39)
@@ -5676,7 +5671,7 @@
 Ольков Г.В., спортзал (№01)</t>
         </is>
       </c>
-      <c r="H38" s="107" t="inlineStr">
+      <c r="H38" s="106" t="inlineStr">
         <is>
           <t>Англ.язык
 Акауова И.Н., нач. класс 3А (№7)</t>
@@ -5721,18 +5716,18 @@
       <c r="O38" s="50" t="inlineStr">
         <is>
           <t>Русский язык
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. английского языка (№27)
 вместе с 6В</t>
         </is>
       </c>
       <c r="P38" s="50" t="inlineStr">
         <is>
           <t>Русский язык
-Темерканова О.В., каб. технологии (мальчики) (№39)
+Темерканова О.В., каб. английского языка (№27)
 вместе с 6Б</t>
         </is>
       </c>
-      <c r="Q38" s="111" t="inlineStr">
+      <c r="Q38" s="110" t="inlineStr">
         <is>
           <t>Всем.история
 Мельникова Л.Р., каб. математики (№25)</t>
@@ -5835,7 +5830,7 @@
 Боранбаев Д.Б., каб. НВП (№28)</t>
         </is>
       </c>
-      <c r="N39" s="106" t="inlineStr">
+      <c r="N39" s="111" t="inlineStr">
         <is>
           <t>Девочки: Худ.труд
 Жукова И.М., каб. технологии (девочки) (№29)
@@ -5864,7 +5859,7 @@
 Бучкова И.О., каб. робототехники (№15)</t>
         </is>
       </c>
-      <c r="S39" s="111" t="inlineStr">
+      <c r="S39" s="110" t="inlineStr">
         <is>
           <t>Всем.история
 Мельникова Л.Р., каб. математики (№25)</t>
@@ -5902,7 +5897,7 @@
       <c r="H40" s="29" t="inlineStr">
         <is>
           <t>Казахский язык
-Дюсембаева А.К., нач. класс 3А (№7)</t>
+Власова А.К., нач. класс 3А (№7)</t>
         </is>
       </c>
       <c r="I40" s="23" t="n"/>
@@ -5942,14 +5937,19 @@
         </is>
       </c>
       <c r="P40" s="23" t="n"/>
-      <c r="Q40" s="23" t="n"/>
+      <c r="Q40" s="52" t="inlineStr">
+        <is>
+          <t>Физика
+Русина Н.В., каб. физики (№16)</t>
+        </is>
+      </c>
       <c r="R40" s="57" t="inlineStr">
         <is>
           <t>Физкультура
 Ольков Г.В., спортзал (№01)</t>
         </is>
       </c>
-      <c r="S40" s="106" t="inlineStr">
+      <c r="S40" s="111" t="inlineStr">
         <is>
           <t>Девочки: Худ.труд
 Жукова И.М., каб. технологии (девочки) (№29)
@@ -6004,7 +6004,7 @@
       <c r="R41" s="23" t="n"/>
       <c r="S41" s="23" t="n"/>
       <c r="T41" s="23" t="n"/>
-      <c r="U41" s="106" t="inlineStr">
+      <c r="U41" s="111" t="inlineStr">
         <is>
           <t>Девочки: Худ.труд
 Жукова И.М., каб. технологии (девочки) (№29)
@@ -6363,13 +6363,13 @@
       <c r="F60" s="133" t="inlineStr"/>
       <c r="G60" s="176" t="inlineStr">
         <is>
-          <t>Дмитриев Е.В. — Русская лит.</t>
+          <t>Власова А.К. — Каз. литература</t>
         </is>
       </c>
       <c r="H60" s="133" t="inlineStr"/>
       <c r="I60" s="177" t="inlineStr">
         <is>
-          <t>Дмитриев Е.В. — Русский язык</t>
+          <t>Власова А.К. — Казахский язык</t>
         </is>
       </c>
       <c r="J60" s="133" t="inlineStr"/>
@@ -6377,25 +6377,25 @@
     <row r="61" ht="24" customHeight="1">
       <c r="C61" s="178" t="inlineStr">
         <is>
-          <t>Досаева М.Х. — Всем.история</t>
+          <t>Власова А.К. — КиЛ</t>
         </is>
       </c>
       <c r="D61" s="133" t="inlineStr"/>
       <c r="E61" s="179" t="inlineStr">
         <is>
-          <t>Досаева М.Х. — История Каз.</t>
+          <t>Дмитриев Е.В. — Русская лит.</t>
         </is>
       </c>
       <c r="F61" s="133" t="inlineStr"/>
       <c r="G61" s="180" t="inlineStr">
         <is>
-          <t>Досаева М.Х. — Основы права</t>
+          <t>Дмитриев Е.В. — Русский язык</t>
         </is>
       </c>
       <c r="H61" s="133" t="inlineStr"/>
       <c r="I61" s="181" t="inlineStr">
         <is>
-          <t>Досаева М.Х. — ОПиБ</t>
+          <t>Досаева М.Х. — Всем.история</t>
         </is>
       </c>
       <c r="J61" s="133" t="inlineStr"/>
@@ -6403,19 +6403,19 @@
     <row r="62" ht="24" customHeight="1">
       <c r="C62" s="182" t="inlineStr">
         <is>
-          <t>Дюсембаева А.К. — Каз. литература</t>
+          <t>Досаева М.Х. — История Каз.</t>
         </is>
       </c>
       <c r="D62" s="133" t="inlineStr"/>
       <c r="E62" s="183" t="inlineStr">
         <is>
-          <t>Дюсембаева А.К. — Казахский язык</t>
+          <t>Досаева М.Х. — Основы права</t>
         </is>
       </c>
       <c r="F62" s="133" t="inlineStr"/>
       <c r="G62" s="184" t="inlineStr">
         <is>
-          <t>Дюсембаева А.К. — КиЛ</t>
+          <t>Досаева М.Х. — ОПиБ</t>
         </is>
       </c>
       <c r="H62" s="133" t="inlineStr"/>
@@ -6847,12 +6847,12 @@
       <c r="D81" s="133" t="n">
         <v>21</v>
       </c>
-      <c r="E81" s="133" t="n">
-        <v>0</v>
+      <c r="E81" s="240" t="n">
+        <v>1</v>
       </c>
       <c r="F81" s="133" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Чт 5</t>
         </is>
       </c>
       <c r="G81" s="133" t="inlineStr"/>
@@ -7259,76 +7259,76 @@
     <row r="95">
       <c r="C95" s="133" t="inlineStr">
         <is>
-          <t>Дмитриев Евгений Владимирович</t>
+          <t>Власова Айгуль Каирбековна</t>
         </is>
       </c>
       <c r="D95" s="133" t="n">
-        <v>24</v>
-      </c>
-      <c r="E95" s="133" t="n">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="E95" s="240" t="n">
+        <v>6</v>
       </c>
       <c r="F95" s="133" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Пн 4, Пн 5, Ср 4, Пт 3, Пт 4, Пт 5</t>
         </is>
       </c>
       <c r="G95" s="133" t="inlineStr"/>
       <c r="H95" s="133" t="inlineStr">
         <is>
-          <t>Пн 1–5, 8 ур.; Вт 1–5, 7–8 ур.; Ср весь день; Чт 1–5, 8 ур.; Пт 1–4, 7–8 ур.</t>
+          <t>без ограничений</t>
         </is>
       </c>
       <c r="I95" s="133" t="inlineStr">
         <is>
-          <t>5 / 4 / 6 / 5 / 4</t>
+          <t>4 / 3 / 3 / 5 / 3</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="C96" s="133" t="inlineStr">
         <is>
-          <t>Досаева Мадина Хайрулловна</t>
+          <t>Дмитриев Евгений Владимирович</t>
         </is>
       </c>
       <c r="D96" s="133" t="n">
         <v>24</v>
       </c>
-      <c r="E96" s="240" t="n">
-        <v>7</v>
+      <c r="E96" s="133" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="133" t="inlineStr">
         <is>
-          <t>Пн 2, Вт 3, Ср 5, Чт 4, Чт 5, Пт 2, Пт 3</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G96" s="133" t="inlineStr"/>
       <c r="H96" s="133" t="inlineStr">
         <is>
-          <t>без ограничений</t>
+          <t>Пн 1–5, 8 ур.; Вт 1–5, 7–8 ур.; Ср весь день; Чт 1–5, 8 ур.; Пт 1–4, 7–8 ур.</t>
         </is>
       </c>
       <c r="I96" s="133" t="inlineStr">
         <is>
-          <t>5 / 6 / 5 / 4 / 4</t>
+          <t>5 / 4 / 6 / 5 / 4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="C97" s="133" t="inlineStr">
         <is>
-          <t>Дюсембаева Айгуль Каирбековна</t>
+          <t>Досаева Мадина Хайрулловна</t>
         </is>
       </c>
       <c r="D97" s="133" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E97" s="240" t="n">
         <v>6</v>
       </c>
       <c r="F97" s="133" t="inlineStr">
         <is>
-          <t>Пн 4, Пн 5, Ср 4, Пт 3, Пт 4, Пт 5</t>
+          <t>Пн 2, Вт 3, Ср 5, Чт 4, Пт 2, Пт 3</t>
         </is>
       </c>
       <c r="G97" s="133" t="inlineStr"/>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="I97" s="133" t="inlineStr">
         <is>
-          <t>4 / 3 / 3 / 5 / 3</t>
+          <t>5 / 6 / 5 / 4 / 4</t>
         </is>
       </c>
     </row>
@@ -7372,7 +7372,7 @@
       </c>
       <c r="I98" s="133" t="inlineStr">
         <is>
-          <t>0 / 0 / 4 / 3 / 5</t>
+          <t>0 / 0 / 3 / 3 / 6</t>
         </is>
       </c>
     </row>
@@ -7448,22 +7448,22 @@
         <v>10</v>
       </c>
       <c r="E101" s="240" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F101" s="133" t="inlineStr">
         <is>
-          <t>Чт 6, Пт 4</t>
+          <t>Ср 3, Ср 4, Ср 5, Чт 6, Пт 4</t>
         </is>
       </c>
       <c r="G101" s="133" t="inlineStr"/>
       <c r="H101" s="133" t="inlineStr">
         <is>
-          <t>Пн 1, 3–8 ур.; Вт 2, 4–8 ур.; Ср 2, 6–8 ур.; Чт 2–8 ур.; Пт весь день</t>
+          <t>Пн 1, 3–8 ур.; Вт 2, 4–8 ур.; Ср 2–8 ур.; Чт 2, 5–8 ур.; Пт весь день</t>
         </is>
       </c>
       <c r="I101" s="133" t="inlineStr">
         <is>
-          <t>0 / 0 / 3 / 2 / 5</t>
+          <t>0 / 0 / 2 / 2 / 6</t>
         </is>
       </c>
     </row>
@@ -7688,7 +7688,7 @@
       </c>
       <c r="F109" s="133" t="inlineStr">
         <is>
-          <t>Пн 5, Вт 5, Ср 2, Ср 3, Ср 4, Чт 2, Чт 3, Чт 4, Чт 5, Пт 5</t>
+          <t>Пн 5, Вт 5, Ср 2, Ср 3, Ср 6, Чт 2, Чт 3, Чт 4, Чт 5, Пт 5</t>
         </is>
       </c>
       <c r="G109" s="133" t="inlineStr"/>
@@ -7771,11 +7771,11 @@
         <v>13</v>
       </c>
       <c r="E112" s="240" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F112" s="133" t="inlineStr">
         <is>
-          <t>Ср 5, Ср 6, Пт 2</t>
+          <t>Ср 5</t>
         </is>
       </c>
       <c r="G112" s="133" t="inlineStr"/>
@@ -8055,9 +8055,9 @@
       </c>
       <c r="E124" s="133" t="inlineStr">
         <is>
-          <t>Ср: 4 ур. 1А Труд. обучение; 4 ур. 7А/Мальчики Худ.труд; 5 ур. 5А,6А,8Ә Худ.труд; 6 ур. 6Б/Мальчики Худ.труд
+          <t>Ср: 4 ур. 1А Труд. обучение; 5 ур. 5А,6А,8Ә Худ.труд; 6 ур. 6Б/Мальчики Худ.труд
 Чт: 2 ур. 1А ИЗО; 5 ур. 5Б/Мальчики Худ.труд; 7 ур. 8А/Мальчики Худ.труд
-Пт: 2 ур. 6Б/Мальчики Худ.труд; 3 ур. 5А,6А Худ.труд; 5 ур. 5Б/Мальчики Худ.труд; 6 ур. 8Б/Мальчики Худ.труд; 7 ур. 9Б/Мальчики Худ.труд</t>
+Пт: 1 ур. 7А/Мальчики Худ.труд; 2 ур. 6Б/Мальчики Худ.труд; 3 ур. 5А,6А Худ.труд; 5 ур. 5Б/Мальчики Худ.труд; 6 ур. 8Б/Мальчики Худ.труд; 7 ур. 9Б/Мальчики Худ.труд</t>
         </is>
       </c>
       <c r="F124" s="133" t="n">
@@ -8732,17 +8732,17 @@
       </c>
       <c r="F146" s="133" t="inlineStr">
         <is>
+          <t>6 (1–6)</t>
+        </is>
+      </c>
+      <c r="G146" s="133" t="inlineStr">
+        <is>
           <t>7 (1–7)</t>
         </is>
       </c>
-      <c r="G146" s="133" t="inlineStr">
-        <is>
-          <t>7 (1–7)</t>
-        </is>
-      </c>
       <c r="H146" s="133" t="inlineStr">
         <is>
-          <t>5 (1–5)</t>
+          <t>6 (1–6)</t>
         </is>
       </c>
       <c r="I146" s="133" t="n">
@@ -9363,13 +9363,17 @@
 каб. робототехники (№15)</t>
         </is>
       </c>
-      <c r="AD3" s="244" t="inlineStr">
+      <c r="AD3" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="AE3" s="244" t="inlineStr">
         <is>
           <t>8Ә
-каб. робототехники (№15)</t>
-        </is>
-      </c>
-      <c r="AE3" s="244" t="n"/>
+каб. истории (№14)</t>
+        </is>
+      </c>
       <c r="AF3" s="244" t="n"/>
       <c r="AG3" s="244" t="n"/>
       <c r="AH3" s="244" t="inlineStr">
@@ -9404,7 +9408,7 @@
         <v>21</v>
       </c>
       <c r="AQ3" s="243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
@@ -9419,7 +9423,7 @@
 нач. класс 1Б (№8)</t>
         </is>
       </c>
-      <c r="C4" s="245" t="n"/>
+      <c r="C4" s="246" t="n"/>
       <c r="D4" s="244" t="inlineStr">
         <is>
           <t>1Б
@@ -9429,7 +9433,7 @@
       <c r="E4" s="244" t="inlineStr">
         <is>
           <t>5Б
-каб. робототехники (№15)</t>
+каб. мультимедийный (№18)</t>
         </is>
       </c>
       <c r="F4" s="244" t="n"/>
@@ -9465,7 +9469,7 @@
 нач. класс 1Б (№8)</t>
         </is>
       </c>
-      <c r="S4" s="245" t="n"/>
+      <c r="S4" s="246" t="n"/>
       <c r="T4" s="244" t="inlineStr">
         <is>
           <t>1Б
@@ -9516,7 +9520,7 @@
 нач. класс 1Б (№8)</t>
         </is>
       </c>
-      <c r="AI4" s="245" t="n"/>
+      <c r="AI4" s="246" t="n"/>
       <c r="AJ4" s="244" t="inlineStr">
         <is>
           <t>1Б
@@ -9603,10 +9607,10 @@
 каб. английского языка (№27)</t>
         </is>
       </c>
-      <c r="N5" s="245" t="n"/>
-      <c r="O5" s="245" t="n"/>
-      <c r="P5" s="245" t="n"/>
-      <c r="Q5" s="245" t="n"/>
+      <c r="N5" s="246" t="n"/>
+      <c r="O5" s="246" t="n"/>
+      <c r="P5" s="246" t="n"/>
+      <c r="Q5" s="246" t="n"/>
       <c r="R5" s="244" t="inlineStr">
         <is>
           <t>4А
@@ -9619,7 +9623,7 @@
 каб. английского языка (№27)</t>
         </is>
       </c>
-      <c r="T5" s="246" t="inlineStr">
+      <c r="T5" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9673,7 +9677,7 @@
 нач. класс 4Б (№9)</t>
         </is>
       </c>
-      <c r="AD5" s="246" t="inlineStr">
+      <c r="AD5" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9705,7 +9709,7 @@
 нач. класс 3А (№7)</t>
         </is>
       </c>
-      <c r="AL5" s="246" t="inlineStr">
+      <c r="AL5" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9743,7 +9747,7 @@
 нач. класс 2А/4А (№42)</t>
         </is>
       </c>
-      <c r="D6" s="246" t="inlineStr">
+      <c r="D6" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9787,7 +9791,7 @@
 нач. класс 2А/4А (№42)</t>
         </is>
       </c>
-      <c r="S6" s="246" t="inlineStr">
+      <c r="S6" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9859,7 +9863,7 @@
 нач. класс 2А/4А (№42)</t>
         </is>
       </c>
-      <c r="AK6" s="246" t="inlineStr">
+      <c r="AK6" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9958,7 +9962,7 @@
 каб. казахского языка и литературы (№23)</t>
         </is>
       </c>
-      <c r="S7" s="246" t="inlineStr">
+      <c r="S7" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -9975,7 +9979,7 @@
 каб. казахского языка (№24)</t>
         </is>
       </c>
-      <c r="V7" s="246" t="inlineStr">
+      <c r="V7" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10012,7 +10016,7 @@
 каб. казахского языка (№24)</t>
         </is>
       </c>
-      <c r="AD7" s="246" t="inlineStr">
+      <c r="AD7" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10048,7 +10052,7 @@
 каб. казахского языка (№24)</t>
         </is>
       </c>
-      <c r="AK7" s="246" t="inlineStr">
+      <c r="AK7" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10093,7 +10097,7 @@
 нач. класс 2Б (№6)</t>
         </is>
       </c>
-      <c r="E8" s="246" t="inlineStr">
+      <c r="E8" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10179,7 +10183,7 @@
 каб. казахского языка (№24)</t>
         </is>
       </c>
-      <c r="AA8" s="245" t="n"/>
+      <c r="AA8" s="246" t="n"/>
       <c r="AB8" s="244" t="inlineStr">
         <is>
           <t>8Б
@@ -10247,22 +10251,22 @@
           <t>Аятова А.Ж.</t>
         </is>
       </c>
-      <c r="B9" s="245" t="n"/>
-      <c r="C9" s="245" t="n"/>
-      <c r="D9" s="245" t="n"/>
-      <c r="E9" s="245" t="n"/>
-      <c r="F9" s="245" t="n"/>
-      <c r="G9" s="245" t="n"/>
-      <c r="H9" s="245" t="n"/>
-      <c r="I9" s="245" t="n"/>
-      <c r="J9" s="245" t="n"/>
-      <c r="K9" s="245" t="n"/>
-      <c r="L9" s="245" t="n"/>
-      <c r="M9" s="245" t="n"/>
-      <c r="N9" s="245" t="n"/>
-      <c r="O9" s="245" t="n"/>
-      <c r="P9" s="245" t="n"/>
-      <c r="Q9" s="245" t="n"/>
+      <c r="B9" s="246" t="n"/>
+      <c r="C9" s="246" t="n"/>
+      <c r="D9" s="246" t="n"/>
+      <c r="E9" s="246" t="n"/>
+      <c r="F9" s="246" t="n"/>
+      <c r="G9" s="246" t="n"/>
+      <c r="H9" s="246" t="n"/>
+      <c r="I9" s="246" t="n"/>
+      <c r="J9" s="246" t="n"/>
+      <c r="K9" s="246" t="n"/>
+      <c r="L9" s="246" t="n"/>
+      <c r="M9" s="246" t="n"/>
+      <c r="N9" s="246" t="n"/>
+      <c r="O9" s="246" t="n"/>
+      <c r="P9" s="246" t="n"/>
+      <c r="Q9" s="246" t="n"/>
       <c r="R9" s="244" t="inlineStr">
         <is>
           <t>8Ә
@@ -10291,22 +10295,22 @@
       <c r="W9" s="244" t="n"/>
       <c r="X9" s="244" t="n"/>
       <c r="Y9" s="244" t="n"/>
-      <c r="Z9" s="245" t="n"/>
-      <c r="AA9" s="245" t="n"/>
-      <c r="AB9" s="245" t="n"/>
-      <c r="AC9" s="245" t="n"/>
-      <c r="AD9" s="245" t="n"/>
-      <c r="AE9" s="245" t="n"/>
-      <c r="AF9" s="245" t="n"/>
-      <c r="AG9" s="245" t="n"/>
-      <c r="AH9" s="245" t="n"/>
-      <c r="AI9" s="245" t="n"/>
-      <c r="AJ9" s="245" t="n"/>
-      <c r="AK9" s="245" t="n"/>
-      <c r="AL9" s="245" t="n"/>
-      <c r="AM9" s="245" t="n"/>
-      <c r="AN9" s="245" t="n"/>
-      <c r="AO9" s="245" t="n"/>
+      <c r="Z9" s="246" t="n"/>
+      <c r="AA9" s="246" t="n"/>
+      <c r="AB9" s="246" t="n"/>
+      <c r="AC9" s="246" t="n"/>
+      <c r="AD9" s="246" t="n"/>
+      <c r="AE9" s="246" t="n"/>
+      <c r="AF9" s="246" t="n"/>
+      <c r="AG9" s="246" t="n"/>
+      <c r="AH9" s="246" t="n"/>
+      <c r="AI9" s="246" t="n"/>
+      <c r="AJ9" s="246" t="n"/>
+      <c r="AK9" s="246" t="n"/>
+      <c r="AL9" s="246" t="n"/>
+      <c r="AM9" s="246" t="n"/>
+      <c r="AN9" s="246" t="n"/>
+      <c r="AO9" s="246" t="n"/>
       <c r="AP9" s="243" t="n">
         <v>4</v>
       </c>
@@ -10366,7 +10370,7 @@
 каб. химии (№17)</t>
         </is>
       </c>
-      <c r="M10" s="246" t="inlineStr">
+      <c r="M10" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10392,7 +10396,7 @@
 каб. биологии (№19)</t>
         </is>
       </c>
-      <c r="T10" s="246" t="inlineStr">
+      <c r="T10" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10424,7 +10428,7 @@
 каб. химии (№17)</t>
         </is>
       </c>
-      <c r="AB10" s="246" t="inlineStr">
+      <c r="AB10" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10490,17 +10494,17 @@
           <t>Байгазиева А.Д.</t>
         </is>
       </c>
-      <c r="B11" s="245" t="n"/>
-      <c r="C11" s="245" t="n"/>
-      <c r="D11" s="245" t="n"/>
-      <c r="E11" s="245" t="n"/>
-      <c r="F11" s="245" t="n"/>
-      <c r="G11" s="245" t="n"/>
-      <c r="H11" s="245" t="n"/>
-      <c r="I11" s="245" t="n"/>
-      <c r="J11" s="245" t="n"/>
-      <c r="K11" s="245" t="n"/>
-      <c r="L11" s="245" t="n"/>
+      <c r="B11" s="246" t="n"/>
+      <c r="C11" s="246" t="n"/>
+      <c r="D11" s="246" t="n"/>
+      <c r="E11" s="246" t="n"/>
+      <c r="F11" s="246" t="n"/>
+      <c r="G11" s="246" t="n"/>
+      <c r="H11" s="246" t="n"/>
+      <c r="I11" s="246" t="n"/>
+      <c r="J11" s="246" t="n"/>
+      <c r="K11" s="246" t="n"/>
+      <c r="L11" s="246" t="n"/>
       <c r="M11" s="244" t="inlineStr">
         <is>
           <t>8Ә
@@ -10513,20 +10517,20 @@
 каб. биологии (№19)</t>
         </is>
       </c>
-      <c r="O11" s="245" t="n"/>
-      <c r="P11" s="245" t="n"/>
-      <c r="Q11" s="245" t="n"/>
-      <c r="R11" s="245" t="n"/>
-      <c r="S11" s="245" t="n"/>
-      <c r="T11" s="245" t="n"/>
-      <c r="U11" s="245" t="n"/>
-      <c r="V11" s="245" t="n"/>
-      <c r="W11" s="245" t="n"/>
-      <c r="X11" s="245" t="n"/>
-      <c r="Y11" s="245" t="n"/>
-      <c r="Z11" s="245" t="n"/>
-      <c r="AA11" s="245" t="n"/>
-      <c r="AB11" s="245" t="n"/>
+      <c r="O11" s="246" t="n"/>
+      <c r="P11" s="246" t="n"/>
+      <c r="Q11" s="246" t="n"/>
+      <c r="R11" s="246" t="n"/>
+      <c r="S11" s="246" t="n"/>
+      <c r="T11" s="246" t="n"/>
+      <c r="U11" s="246" t="n"/>
+      <c r="V11" s="246" t="n"/>
+      <c r="W11" s="246" t="n"/>
+      <c r="X11" s="246" t="n"/>
+      <c r="Y11" s="246" t="n"/>
+      <c r="Z11" s="246" t="n"/>
+      <c r="AA11" s="246" t="n"/>
+      <c r="AB11" s="246" t="n"/>
       <c r="AC11" s="244" t="inlineStr">
         <is>
           <t>8Ә
@@ -10539,17 +10543,17 @@
 каб. биологии (№19)</t>
         </is>
       </c>
-      <c r="AE11" s="245" t="n"/>
-      <c r="AF11" s="245" t="n"/>
-      <c r="AG11" s="245" t="n"/>
-      <c r="AH11" s="245" t="n"/>
-      <c r="AI11" s="245" t="n"/>
-      <c r="AJ11" s="245" t="n"/>
-      <c r="AK11" s="245" t="n"/>
-      <c r="AL11" s="245" t="n"/>
-      <c r="AM11" s="245" t="n"/>
-      <c r="AN11" s="245" t="n"/>
-      <c r="AO11" s="245" t="n"/>
+      <c r="AE11" s="246" t="n"/>
+      <c r="AF11" s="246" t="n"/>
+      <c r="AG11" s="246" t="n"/>
+      <c r="AH11" s="246" t="n"/>
+      <c r="AI11" s="246" t="n"/>
+      <c r="AJ11" s="246" t="n"/>
+      <c r="AK11" s="246" t="n"/>
+      <c r="AL11" s="246" t="n"/>
+      <c r="AM11" s="246" t="n"/>
+      <c r="AN11" s="246" t="n"/>
+      <c r="AO11" s="246" t="n"/>
       <c r="AP11" s="243" t="n">
         <v>4</v>
       </c>
@@ -10653,7 +10657,7 @@
 каб. казахского языка и литературы (№23)</t>
         </is>
       </c>
-      <c r="V12" s="246" t="inlineStr">
+      <c r="V12" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10705,12 +10709,12 @@
 каб. казахского языка и литературы (№23)</t>
         </is>
       </c>
-      <c r="AI12" s="246" t="inlineStr">
+      <c r="AI12" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="AJ12" s="246" t="inlineStr">
+      <c r="AJ12" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10748,8 +10752,8 @@
           <t>Балташева З.Т.</t>
         </is>
       </c>
-      <c r="B13" s="245" t="n"/>
-      <c r="C13" s="245" t="n"/>
+      <c r="B13" s="246" t="n"/>
+      <c r="C13" s="246" t="n"/>
       <c r="D13" s="244" t="inlineStr">
         <is>
           <t>8Ә
@@ -10776,38 +10780,38 @@
       </c>
       <c r="H13" s="244" t="n"/>
       <c r="I13" s="244" t="n"/>
-      <c r="J13" s="245" t="n"/>
-      <c r="K13" s="245" t="n"/>
-      <c r="L13" s="245" t="n"/>
-      <c r="M13" s="245" t="n"/>
-      <c r="N13" s="245" t="n"/>
-      <c r="O13" s="245" t="n"/>
-      <c r="P13" s="245" t="n"/>
-      <c r="Q13" s="245" t="n"/>
-      <c r="R13" s="245" t="n"/>
-      <c r="S13" s="245" t="n"/>
-      <c r="T13" s="245" t="n"/>
-      <c r="U13" s="245" t="n"/>
-      <c r="V13" s="245" t="n"/>
-      <c r="W13" s="245" t="n"/>
-      <c r="X13" s="245" t="n"/>
-      <c r="Y13" s="245" t="n"/>
-      <c r="Z13" s="245" t="n"/>
-      <c r="AA13" s="245" t="n"/>
-      <c r="AB13" s="245" t="n"/>
-      <c r="AC13" s="245" t="n"/>
-      <c r="AD13" s="245" t="n"/>
-      <c r="AE13" s="245" t="n"/>
-      <c r="AF13" s="245" t="n"/>
-      <c r="AG13" s="245" t="n"/>
-      <c r="AH13" s="245" t="n"/>
-      <c r="AI13" s="245" t="n"/>
-      <c r="AJ13" s="245" t="n"/>
-      <c r="AK13" s="245" t="n"/>
-      <c r="AL13" s="245" t="n"/>
-      <c r="AM13" s="245" t="n"/>
-      <c r="AN13" s="245" t="n"/>
-      <c r="AO13" s="245" t="n"/>
+      <c r="J13" s="246" t="n"/>
+      <c r="K13" s="246" t="n"/>
+      <c r="L13" s="246" t="n"/>
+      <c r="M13" s="246" t="n"/>
+      <c r="N13" s="246" t="n"/>
+      <c r="O13" s="246" t="n"/>
+      <c r="P13" s="246" t="n"/>
+      <c r="Q13" s="246" t="n"/>
+      <c r="R13" s="246" t="n"/>
+      <c r="S13" s="246" t="n"/>
+      <c r="T13" s="246" t="n"/>
+      <c r="U13" s="246" t="n"/>
+      <c r="V13" s="246" t="n"/>
+      <c r="W13" s="246" t="n"/>
+      <c r="X13" s="246" t="n"/>
+      <c r="Y13" s="246" t="n"/>
+      <c r="Z13" s="246" t="n"/>
+      <c r="AA13" s="246" t="n"/>
+      <c r="AB13" s="246" t="n"/>
+      <c r="AC13" s="246" t="n"/>
+      <c r="AD13" s="246" t="n"/>
+      <c r="AE13" s="246" t="n"/>
+      <c r="AF13" s="246" t="n"/>
+      <c r="AG13" s="246" t="n"/>
+      <c r="AH13" s="246" t="n"/>
+      <c r="AI13" s="246" t="n"/>
+      <c r="AJ13" s="246" t="n"/>
+      <c r="AK13" s="246" t="n"/>
+      <c r="AL13" s="246" t="n"/>
+      <c r="AM13" s="246" t="n"/>
+      <c r="AN13" s="246" t="n"/>
+      <c r="AO13" s="246" t="n"/>
       <c r="AP13" s="243" t="n">
         <v>4</v>
       </c>
@@ -10839,7 +10843,7 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="E14" s="246" t="inlineStr">
+      <c r="E14" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10870,7 +10874,7 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="L14" s="246" t="inlineStr">
+      <c r="L14" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10881,7 +10885,7 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="N14" s="246" t="inlineStr">
+      <c r="N14" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10955,18 +10959,18 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="AC14" s="245" t="n"/>
-      <c r="AD14" s="245" t="n"/>
-      <c r="AE14" s="245" t="n"/>
-      <c r="AF14" s="245" t="n"/>
-      <c r="AG14" s="245" t="n"/>
+      <c r="AC14" s="246" t="n"/>
+      <c r="AD14" s="246" t="n"/>
+      <c r="AE14" s="246" t="n"/>
+      <c r="AF14" s="246" t="n"/>
+      <c r="AG14" s="246" t="n"/>
       <c r="AH14" s="244" t="inlineStr">
         <is>
           <t>5Б
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="AI14" s="246" t="inlineStr">
+      <c r="AI14" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -10977,7 +10981,7 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="AK14" s="246" t="inlineStr">
+      <c r="AK14" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11086,7 +11090,7 @@
 каб. робототехники (№15)</t>
         </is>
       </c>
-      <c r="F16" s="246" t="inlineStr">
+      <c r="F16" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11181,497 +11185,492 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="243" t="inlineStr">
         <is>
-          <t>Дмитриев Е.В.</t>
+          <t>Власова А.К.</t>
         </is>
       </c>
       <c r="B17" s="244" t="inlineStr">
         <is>
-          <t>9Б
-каб. русского языка (№20)</t>
+          <t>8А
+каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="C17" s="244" t="inlineStr">
         <is>
-          <t>11Б
-каб. русского языка (№20)</t>
+          <t>1Б
+нач. класс 1Б (№8)</t>
         </is>
       </c>
       <c r="D17" s="244" t="inlineStr">
         <is>
-          <t>8А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="E17" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="F17" s="244" t="inlineStr">
-        <is>
-          <t>10А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="G17" s="245" t="n"/>
-      <c r="H17" s="245" t="n"/>
+          <t>3А
+нач. класс 3А (№7)</t>
+        </is>
+      </c>
+      <c r="E17" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="F17" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="G17" s="244" t="inlineStr">
+        <is>
+          <t>8Ә
+каб. НВП (№28)</t>
+        </is>
+      </c>
+      <c r="H17" s="244" t="n"/>
       <c r="I17" s="244" t="n"/>
       <c r="J17" s="244" t="n"/>
-      <c r="K17" s="244" t="n"/>
+      <c r="K17" s="244" t="inlineStr">
+        <is>
+          <t>7А
+каб. физики (№16)</t>
+        </is>
+      </c>
       <c r="L17" s="244" t="inlineStr">
         <is>
+          <t>8Ә
+каб. физики (№16)</t>
+        </is>
+      </c>
+      <c r="M17" s="244" t="inlineStr">
+        <is>
+          <t>8А
+каб. физики (№16)</t>
+        </is>
+      </c>
+      <c r="N17" s="244" t="n"/>
+      <c r="O17" s="244" t="n"/>
+      <c r="P17" s="244" t="n"/>
+      <c r="Q17" s="244" t="n"/>
+      <c r="R17" s="244" t="n"/>
+      <c r="S17" s="244" t="n"/>
+      <c r="T17" s="244" t="inlineStr">
+        <is>
+          <t>8А
+каб. английского языка (№27)</t>
+        </is>
+      </c>
+      <c r="U17" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="V17" s="244" t="inlineStr">
+        <is>
           <t>7А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="M17" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="N17" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="O17" s="245" t="n"/>
-      <c r="P17" s="244" t="inlineStr">
-        <is>
-          <t>8А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="Q17" s="244" t="n"/>
-      <c r="R17" s="244" t="inlineStr">
-        <is>
-          <t>8А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="S17" s="244" t="inlineStr">
-        <is>
-          <t>7А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="T17" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="U17" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="V17" s="244" t="inlineStr">
-        <is>
-          <t>10А
-каб. русского языка (№20)</t>
+каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="W17" s="244" t="inlineStr">
         <is>
-          <t>8Б
-каб. русского языка (№20)</t>
+          <t>8Ә
+каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="X17" s="244" t="n"/>
       <c r="Y17" s="244" t="n"/>
       <c r="Z17" s="244" t="inlineStr">
         <is>
-          <t>8Б
-каб. русского языка (№20)</t>
+          <t>8Ә
+каб. НВП (№28)</t>
         </is>
       </c>
       <c r="AA17" s="244" t="inlineStr">
         <is>
-          <t>9Б
-каб. русского языка (№20)</t>
+          <t>7А
+каб. НВП (№28)</t>
         </is>
       </c>
       <c r="AB17" s="244" t="inlineStr">
         <is>
+          <t>1Б
+нач. класс 1Б (№8)</t>
+        </is>
+      </c>
+      <c r="AC17" s="244" t="inlineStr">
+        <is>
+          <t>3А
+нач. класс 3А (№7)</t>
+        </is>
+      </c>
+      <c r="AD17" s="244" t="inlineStr">
+        <is>
           <t>8А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="AC17" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="AD17" s="244" t="inlineStr">
-        <is>
-          <t>7А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="AE17" s="245" t="n"/>
-      <c r="AF17" s="245" t="n"/>
+каб. английского языка (№27)</t>
+        </is>
+      </c>
+      <c r="AE17" s="244" t="n"/>
+      <c r="AF17" s="244" t="n"/>
       <c r="AG17" s="244" t="n"/>
       <c r="AH17" s="244" t="inlineStr">
         <is>
-          <t>8А
-каб. русского языка (№20)</t>
+          <t>8Ә
+каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="AI17" s="244" t="inlineStr">
         <is>
-          <t>9Б
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="AJ17" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="AK17" s="244" t="inlineStr">
-        <is>
-          <t>10А
-каб. русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="AL17" s="245" t="n"/>
-      <c r="AM17" s="245" t="n"/>
+          <t>7А
+каб. английского языка (№27)</t>
+        </is>
+      </c>
+      <c r="AJ17" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="AK17" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="AL17" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="AM17" s="244" t="inlineStr">
+        <is>
+          <t>3А
+нач. класс 3А (№7)</t>
+        </is>
+      </c>
       <c r="AN17" s="244" t="n"/>
       <c r="AO17" s="244" t="n"/>
       <c r="AP17" s="243" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AQ17" s="243" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="243" t="inlineStr">
         <is>
-          <t>Досаева М.Х.</t>
+          <t>Дмитриев Е.В.</t>
         </is>
       </c>
       <c r="B18" s="244" t="inlineStr">
         <is>
-          <t>5А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="C18" s="246" t="inlineStr">
-        <is>
-          <t>окно</t>
+          <t>9Б
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="C18" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+каб. русского языка (№20)</t>
         </is>
       </c>
       <c r="D18" s="244" t="inlineStr">
         <is>
-          <t>6А
-каб. истории (№14)</t>
+          <t>8А
+каб. русского языка (№20)</t>
         </is>
       </c>
       <c r="E18" s="244" t="inlineStr">
         <is>
-          <t>11А
-каб. истории (№14)</t>
+          <t>8Б
+каб. русского языка (№20)</t>
         </is>
       </c>
       <c r="F18" s="244" t="inlineStr">
         <is>
+          <t>10А
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="G18" s="246" t="n"/>
+      <c r="H18" s="246" t="n"/>
+      <c r="I18" s="244" t="n"/>
+      <c r="J18" s="244" t="n"/>
+      <c r="K18" s="244" t="n"/>
+      <c r="L18" s="244" t="inlineStr">
+        <is>
+          <t>7А
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="M18" s="244" t="inlineStr">
+        <is>
           <t>9Б
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="G18" s="244" t="inlineStr">
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="N18" s="244" t="inlineStr">
         <is>
           <t>8Б
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="H18" s="244" t="n"/>
-      <c r="I18" s="244" t="n"/>
-      <c r="J18" s="244" t="inlineStr">
-        <is>
-          <t>5А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="K18" s="244" t="inlineStr">
-        <is>
-          <t>11А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="L18" s="246" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="M18" s="244" t="inlineStr">
-        <is>
-          <t>7А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="N18" s="244" t="inlineStr">
-        <is>
-          <t>6А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="O18" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-каб. истории (№14)</t>
-        </is>
-      </c>
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="O18" s="246" t="n"/>
       <c r="P18" s="244" t="inlineStr">
         <is>
-          <t>9Б
-каб. истории (№14)</t>
+          <t>8А
+каб. русского языка (№20)</t>
         </is>
       </c>
       <c r="Q18" s="244" t="n"/>
       <c r="R18" s="244" t="inlineStr">
         <is>
+          <t>8А
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="S18" s="244" t="inlineStr">
+        <is>
+          <t>7А
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="T18" s="244" t="inlineStr">
+        <is>
           <t>9Б
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="S18" s="244" t="inlineStr">
-        <is>
-          <t>6А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="T18" s="244" t="inlineStr">
-        <is>
-          <t>8Ә
-каб. истории (№14)</t>
+каб. русского языка (№20)</t>
         </is>
       </c>
       <c r="U18" s="244" t="inlineStr">
         <is>
+          <t>11Б
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="V18" s="244" t="inlineStr">
+        <is>
+          <t>10А
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="W18" s="244" t="inlineStr">
+        <is>
           <t>8Б
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="V18" s="246" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="W18" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-каб. истории (№14)</t>
+каб. русского языка (№20)</t>
         </is>
       </c>
       <c r="X18" s="244" t="n"/>
       <c r="Y18" s="244" t="n"/>
       <c r="Z18" s="244" t="inlineStr">
         <is>
+          <t>8Б
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="AA18" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="AB18" s="244" t="inlineStr">
+        <is>
+          <t>8А
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="AC18" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="AD18" s="244" t="inlineStr">
+        <is>
           <t>7А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="AA18" s="244" t="inlineStr">
-        <is>
-          <t>11А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="AB18" s="244" t="inlineStr">
-        <is>
-          <t>5А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="AC18" s="246" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="AD18" s="246" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="AE18" s="244" t="inlineStr">
-        <is>
-          <t>8Ә
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="AF18" s="244" t="n"/>
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="AE18" s="246" t="n"/>
+      <c r="AF18" s="246" t="n"/>
       <c r="AG18" s="244" t="n"/>
       <c r="AH18" s="244" t="inlineStr">
         <is>
-          <t>11А
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="AI18" s="246" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="AJ18" s="246" t="inlineStr">
-        <is>
-          <t>окно</t>
+          <t>8А
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="AI18" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="AJ18" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+каб. русского языка (№20)</t>
         </is>
       </c>
       <c r="AK18" s="244" t="inlineStr">
         <is>
-          <t>8Ә
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="AL18" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="AM18" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-каб. истории (№14)</t>
-        </is>
-      </c>
+          <t>10А
+каб. русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="AL18" s="246" t="n"/>
+      <c r="AM18" s="246" t="n"/>
       <c r="AN18" s="244" t="n"/>
       <c r="AO18" s="244" t="n"/>
       <c r="AP18" s="243" t="n">
         <v>24</v>
       </c>
       <c r="AQ18" s="243" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="243" t="inlineStr">
         <is>
-          <t>Дюсембаева А.К.</t>
+          <t>Досаева М.Х.</t>
         </is>
       </c>
       <c r="B19" s="244" t="inlineStr">
         <is>
-          <t>8А
-каб. английского языка (№27)</t>
-        </is>
-      </c>
-      <c r="C19" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-нач. класс 1Б (№8)</t>
+          <t>5А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="C19" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
         </is>
       </c>
       <c r="D19" s="244" t="inlineStr">
         <is>
-          <t>3А
-нач. класс 3А (№7)</t>
-        </is>
-      </c>
-      <c r="E19" s="246" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="F19" s="246" t="inlineStr">
-        <is>
-          <t>окно</t>
+          <t>6А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="E19" s="244" t="inlineStr">
+        <is>
+          <t>11А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="F19" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+каб. истории (№14)</t>
         </is>
       </c>
       <c r="G19" s="244" t="inlineStr">
         <is>
-          <t>8Ә
-каб. НВП (№28)</t>
+          <t>8Б
+каб. истории (№14)</t>
         </is>
       </c>
       <c r="H19" s="244" t="n"/>
       <c r="I19" s="244" t="n"/>
-      <c r="J19" s="244" t="n"/>
+      <c r="J19" s="244" t="inlineStr">
+        <is>
+          <t>5А
+каб. истории (№14)</t>
+        </is>
+      </c>
       <c r="K19" s="244" t="inlineStr">
         <is>
+          <t>11А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="L19" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="M19" s="244" t="inlineStr">
+        <is>
           <t>7А
-каб. физики (№16)</t>
-        </is>
-      </c>
-      <c r="L19" s="244" t="inlineStr">
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="N19" s="244" t="inlineStr">
+        <is>
+          <t>6А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="O19" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="P19" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="Q19" s="244" t="n"/>
+      <c r="R19" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="S19" s="244" t="inlineStr">
+        <is>
+          <t>6А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="T19" s="244" t="inlineStr">
         <is>
           <t>8Ә
-каб. физики (№16)</t>
-        </is>
-      </c>
-      <c r="M19" s="244" t="inlineStr">
-        <is>
-          <t>8А
-каб. физики (№16)</t>
-        </is>
-      </c>
-      <c r="N19" s="244" t="n"/>
-      <c r="O19" s="244" t="n"/>
-      <c r="P19" s="244" t="n"/>
-      <c r="Q19" s="244" t="n"/>
-      <c r="R19" s="244" t="n"/>
-      <c r="S19" s="244" t="n"/>
-      <c r="T19" s="244" t="inlineStr">
-        <is>
-          <t>8А
-каб. английского языка (№27)</t>
-        </is>
-      </c>
-      <c r="U19" s="246" t="inlineStr">
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="U19" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="V19" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="V19" s="244" t="inlineStr">
-        <is>
-          <t>7А
-каб. английского языка (№27)</t>
-        </is>
-      </c>
       <c r="W19" s="244" t="inlineStr">
         <is>
-          <t>8Ә
-каб. английского языка (№27)</t>
+          <t>11Б
+каб. истории (№14)</t>
         </is>
       </c>
       <c r="X19" s="244" t="n"/>
       <c r="Y19" s="244" t="n"/>
       <c r="Z19" s="244" t="inlineStr">
         <is>
+          <t>7А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="AA19" s="244" t="inlineStr">
+        <is>
+          <t>11А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="AB19" s="244" t="inlineStr">
+        <is>
+          <t>5А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="AC19" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="AD19" s="244" t="inlineStr">
+        <is>
           <t>8Ә
-каб. НВП (№28)</t>
-        </is>
-      </c>
-      <c r="AA19" s="244" t="inlineStr">
-        <is>
-          <t>7А
-каб. НВП (№28)</t>
-        </is>
-      </c>
-      <c r="AB19" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-нач. класс 1Б (№8)</t>
-        </is>
-      </c>
-      <c r="AC19" s="244" t="inlineStr">
-        <is>
-          <t>3А
-нач. класс 3А (№7)</t>
-        </is>
-      </c>
-      <c r="AD19" s="244" t="inlineStr">
-        <is>
-          <t>8А
-каб. английского языка (№27)</t>
+каб. истории (№14)</t>
         </is>
       </c>
       <c r="AE19" s="244" t="n"/>
@@ -11679,41 +11678,42 @@
       <c r="AG19" s="244" t="n"/>
       <c r="AH19" s="244" t="inlineStr">
         <is>
+          <t>11А
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="AI19" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="AJ19" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="AK19" s="244" t="inlineStr">
+        <is>
           <t>8Ә
-каб. английского языка (№27)</t>
-        </is>
-      </c>
-      <c r="AI19" s="244" t="inlineStr">
-        <is>
-          <t>7А
-каб. английского языка (№27)</t>
-        </is>
-      </c>
-      <c r="AJ19" s="246" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="AK19" s="246" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="AL19" s="246" t="inlineStr">
-        <is>
-          <t>окно</t>
+каб. истории (№14)</t>
+        </is>
+      </c>
+      <c r="AL19" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+каб. истории (№14)</t>
         </is>
       </c>
       <c r="AM19" s="244" t="inlineStr">
         <is>
-          <t>3А
-нач. класс 3А (№7)</t>
+          <t>9Б
+каб. истории (№14)</t>
         </is>
       </c>
       <c r="AN19" s="244" t="n"/>
       <c r="AO19" s="244" t="n"/>
       <c r="AP19" s="243" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AQ19" s="243" t="n">
         <v>6</v>
@@ -11725,28 +11725,28 @@
           <t>Жантимиров А.К.</t>
         </is>
       </c>
-      <c r="B20" s="245" t="n"/>
-      <c r="C20" s="245" t="n"/>
-      <c r="D20" s="245" t="n"/>
-      <c r="E20" s="245" t="n"/>
-      <c r="F20" s="245" t="n"/>
-      <c r="G20" s="245" t="n"/>
-      <c r="H20" s="245" t="n"/>
-      <c r="I20" s="245" t="n"/>
-      <c r="J20" s="245" t="n"/>
-      <c r="K20" s="245" t="n"/>
-      <c r="L20" s="245" t="n"/>
-      <c r="M20" s="245" t="n"/>
-      <c r="N20" s="245" t="n"/>
-      <c r="O20" s="245" t="n"/>
-      <c r="P20" s="245" t="n"/>
-      <c r="Q20" s="245" t="n"/>
+      <c r="B20" s="246" t="n"/>
+      <c r="C20" s="246" t="n"/>
+      <c r="D20" s="246" t="n"/>
+      <c r="E20" s="246" t="n"/>
+      <c r="F20" s="246" t="n"/>
+      <c r="G20" s="246" t="n"/>
+      <c r="H20" s="246" t="n"/>
+      <c r="I20" s="246" t="n"/>
+      <c r="J20" s="246" t="n"/>
+      <c r="K20" s="246" t="n"/>
+      <c r="L20" s="246" t="n"/>
+      <c r="M20" s="246" t="n"/>
+      <c r="N20" s="246" t="n"/>
+      <c r="O20" s="246" t="n"/>
+      <c r="P20" s="246" t="n"/>
+      <c r="Q20" s="246" t="n"/>
       <c r="R20" s="244" t="n"/>
       <c r="S20" s="244" t="n"/>
       <c r="T20" s="244" t="n"/>
       <c r="U20" s="244" t="inlineStr">
         <is>
-          <t>7А/Мальчики
+          <t>1А
 каб. технологии (мальчики) (№39)</t>
         </is>
       </c>
@@ -11771,12 +11771,12 @@
 каб. технологии (мальчики) (№39)</t>
         </is>
       </c>
-      <c r="AB20" s="246" t="inlineStr">
+      <c r="AB20" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="AC20" s="246" t="inlineStr">
+      <c r="AC20" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11787,7 +11787,7 @@
 каб. технологии (мальчики) (№39)</t>
         </is>
       </c>
-      <c r="AE20" s="246" t="inlineStr">
+      <c r="AE20" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11799,7 +11799,12 @@
         </is>
       </c>
       <c r="AG20" s="244" t="n"/>
-      <c r="AH20" s="244" t="n"/>
+      <c r="AH20" s="244" t="inlineStr">
+        <is>
+          <t>7А/Мальчики
+каб. технологии (мальчики) (№39)</t>
+        </is>
+      </c>
       <c r="AI20" s="244" t="inlineStr">
         <is>
           <t>6Б/Мальчики
@@ -11812,7 +11817,7 @@
 каб. технологии (мальчики) (№39)</t>
         </is>
       </c>
-      <c r="AK20" s="246" t="inlineStr">
+      <c r="AK20" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11837,7 +11842,7 @@
       </c>
       <c r="AO20" s="244" t="n"/>
       <c r="AP20" s="243" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ20" s="243" t="n">
         <v>4</v>
@@ -11849,21 +11854,21 @@
           <t>Жантимиров Э.А.</t>
         </is>
       </c>
-      <c r="B21" s="245" t="n"/>
-      <c r="C21" s="245" t="n"/>
-      <c r="D21" s="245" t="n"/>
-      <c r="E21" s="245" t="n"/>
-      <c r="F21" s="245" t="n"/>
-      <c r="G21" s="245" t="n"/>
-      <c r="H21" s="245" t="n"/>
-      <c r="I21" s="245" t="n"/>
+      <c r="B21" s="246" t="n"/>
+      <c r="C21" s="246" t="n"/>
+      <c r="D21" s="246" t="n"/>
+      <c r="E21" s="246" t="n"/>
+      <c r="F21" s="246" t="n"/>
+      <c r="G21" s="246" t="n"/>
+      <c r="H21" s="246" t="n"/>
+      <c r="I21" s="246" t="n"/>
       <c r="J21" s="244" t="inlineStr">
         <is>
           <t>2А
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="K21" s="246" t="inlineStr">
+      <c r="K21" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11874,7 +11879,7 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="M21" s="246" t="inlineStr">
+      <c r="M21" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11885,7 +11890,7 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="O21" s="246" t="inlineStr">
+      <c r="O21" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11897,22 +11902,22 @@
         </is>
       </c>
       <c r="Q21" s="244" t="n"/>
-      <c r="R21" s="245" t="n"/>
-      <c r="S21" s="245" t="n"/>
-      <c r="T21" s="245" t="n"/>
-      <c r="U21" s="245" t="n"/>
-      <c r="V21" s="245" t="n"/>
-      <c r="W21" s="245" t="n"/>
-      <c r="X21" s="245" t="n"/>
-      <c r="Y21" s="245" t="n"/>
-      <c r="Z21" s="245" t="n"/>
-      <c r="AA21" s="245" t="n"/>
-      <c r="AB21" s="245" t="n"/>
-      <c r="AC21" s="245" t="n"/>
-      <c r="AD21" s="245" t="n"/>
-      <c r="AE21" s="245" t="n"/>
-      <c r="AF21" s="245" t="n"/>
-      <c r="AG21" s="245" t="n"/>
+      <c r="R21" s="246" t="n"/>
+      <c r="S21" s="246" t="n"/>
+      <c r="T21" s="246" t="n"/>
+      <c r="U21" s="246" t="n"/>
+      <c r="V21" s="246" t="n"/>
+      <c r="W21" s="246" t="n"/>
+      <c r="X21" s="246" t="n"/>
+      <c r="Y21" s="246" t="n"/>
+      <c r="Z21" s="246" t="n"/>
+      <c r="AA21" s="246" t="n"/>
+      <c r="AB21" s="246" t="n"/>
+      <c r="AC21" s="246" t="n"/>
+      <c r="AD21" s="246" t="n"/>
+      <c r="AE21" s="246" t="n"/>
+      <c r="AF21" s="246" t="n"/>
+      <c r="AG21" s="246" t="n"/>
       <c r="AH21" s="244" t="n"/>
       <c r="AI21" s="244" t="inlineStr">
         <is>
@@ -11920,7 +11925,7 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="AJ21" s="246" t="inlineStr">
+      <c r="AJ21" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -11931,12 +11936,12 @@
 каб. информатики (№26)</t>
         </is>
       </c>
-      <c r="AL21" s="246" t="inlineStr">
+      <c r="AL21" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="AM21" s="246" t="inlineStr">
+      <c r="AM21" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -12043,7 +12048,7 @@
       <c r="U22" s="244" t="inlineStr">
         <is>
           <t>2А
-каб. технологии (девочки) (№29)</t>
+нач. класс 2А/4А (№42)</t>
         </is>
       </c>
       <c r="V22" s="244" t="inlineStr">
@@ -12130,67 +12135,79 @@
         </is>
       </c>
       <c r="B23" s="244" t="n"/>
-      <c r="C23" s="245" t="n"/>
+      <c r="C23" s="246" t="n"/>
       <c r="D23" s="244" t="n"/>
       <c r="E23" s="244" t="n"/>
       <c r="F23" s="244" t="n"/>
       <c r="G23" s="244" t="n"/>
       <c r="H23" s="244" t="n"/>
       <c r="I23" s="244" t="n"/>
-      <c r="J23" s="245" t="n"/>
+      <c r="J23" s="246" t="n"/>
       <c r="K23" s="244" t="n"/>
-      <c r="L23" s="245" t="n"/>
+      <c r="L23" s="246" t="n"/>
       <c r="M23" s="244" t="n"/>
       <c r="N23" s="244" t="n"/>
       <c r="O23" s="244" t="n"/>
       <c r="P23" s="244" t="n"/>
       <c r="Q23" s="244" t="n"/>
-      <c r="R23" s="245" t="n"/>
+      <c r="R23" s="246" t="n"/>
       <c r="S23" s="244" t="inlineStr">
         <is>
           <t>2Б
 каб. технологии (девочки) (№29)</t>
         </is>
       </c>
-      <c r="T23" s="245" t="n"/>
-      <c r="U23" s="244" t="inlineStr">
+      <c r="T23" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="U23" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="V23" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="W23" s="244" t="inlineStr">
+        <is>
+          <t>6Б/Девочки
+каб. технологии (девочки) (№29)</t>
+        </is>
+      </c>
+      <c r="X23" s="244" t="n"/>
+      <c r="Y23" s="244" t="n"/>
+      <c r="Z23" s="246" t="n"/>
+      <c r="AA23" s="244" t="n"/>
+      <c r="AB23" s="246" t="n"/>
+      <c r="AC23" s="246" t="n"/>
+      <c r="AD23" s="244" t="inlineStr">
+        <is>
+          <t>5Б/Девочки
+каб. технологии (девочки) (№29)</t>
+        </is>
+      </c>
+      <c r="AE23" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
+        </is>
+      </c>
+      <c r="AF23" s="244" t="inlineStr">
+        <is>
+          <t>8А/Девочки
+каб. технологии (девочки) (№29)</t>
+        </is>
+      </c>
+      <c r="AG23" s="244" t="n"/>
+      <c r="AH23" s="244" t="inlineStr">
         <is>
           <t>7А/Девочки
 каб. технологии (девочки) (№29)</t>
         </is>
       </c>
-      <c r="V23" s="245" t="n"/>
-      <c r="W23" s="244" t="inlineStr">
-        <is>
-          <t>6Б/Девочки
-каб. технологии (девочки) (№29)</t>
-        </is>
-      </c>
-      <c r="X23" s="244" t="n"/>
-      <c r="Y23" s="244" t="n"/>
-      <c r="Z23" s="245" t="n"/>
-      <c r="AA23" s="244" t="n"/>
-      <c r="AB23" s="244" t="n"/>
-      <c r="AC23" s="244" t="n"/>
-      <c r="AD23" s="244" t="inlineStr">
-        <is>
-          <t>5Б/Девочки
-каб. технологии (девочки) (№29)</t>
-        </is>
-      </c>
-      <c r="AE23" s="246" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="AF23" s="244" t="inlineStr">
-        <is>
-          <t>8А/Девочки
-каб. технологии (девочки) (№29)</t>
-        </is>
-      </c>
-      <c r="AG23" s="244" t="n"/>
-      <c r="AH23" s="244" t="n"/>
       <c r="AI23" s="244" t="inlineStr">
         <is>
           <t>6Б/Девочки,6В
@@ -12203,7 +12220,7 @@
 каб. технологии (девочки) (№29)</t>
         </is>
       </c>
-      <c r="AK23" s="246" t="inlineStr">
+      <c r="AK23" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -12231,7 +12248,7 @@
         <v>10</v>
       </c>
       <c r="AQ23" s="243" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
@@ -12252,36 +12269,36 @@
 каб. робототехники (№15)</t>
         </is>
       </c>
-      <c r="D24" s="245" t="n"/>
-      <c r="E24" s="245" t="n"/>
-      <c r="F24" s="245" t="n"/>
-      <c r="G24" s="245" t="n"/>
-      <c r="H24" s="245" t="n"/>
-      <c r="I24" s="245" t="n"/>
-      <c r="J24" s="245" t="n"/>
-      <c r="K24" s="245" t="n"/>
-      <c r="L24" s="245" t="n"/>
-      <c r="M24" s="245" t="n"/>
-      <c r="N24" s="245" t="n"/>
-      <c r="O24" s="245" t="n"/>
-      <c r="P24" s="245" t="n"/>
-      <c r="Q24" s="245" t="n"/>
-      <c r="R24" s="245" t="n"/>
-      <c r="S24" s="245" t="n"/>
-      <c r="T24" s="245" t="n"/>
-      <c r="U24" s="245" t="n"/>
-      <c r="V24" s="245" t="n"/>
-      <c r="W24" s="245" t="n"/>
-      <c r="X24" s="245" t="n"/>
-      <c r="Y24" s="245" t="n"/>
-      <c r="Z24" s="245" t="n"/>
-      <c r="AA24" s="245" t="n"/>
-      <c r="AB24" s="245" t="n"/>
-      <c r="AC24" s="245" t="n"/>
-      <c r="AD24" s="245" t="n"/>
-      <c r="AE24" s="245" t="n"/>
-      <c r="AF24" s="245" t="n"/>
-      <c r="AG24" s="245" t="n"/>
+      <c r="D24" s="246" t="n"/>
+      <c r="E24" s="246" t="n"/>
+      <c r="F24" s="246" t="n"/>
+      <c r="G24" s="246" t="n"/>
+      <c r="H24" s="246" t="n"/>
+      <c r="I24" s="246" t="n"/>
+      <c r="J24" s="246" t="n"/>
+      <c r="K24" s="246" t="n"/>
+      <c r="L24" s="246" t="n"/>
+      <c r="M24" s="246" t="n"/>
+      <c r="N24" s="246" t="n"/>
+      <c r="O24" s="246" t="n"/>
+      <c r="P24" s="246" t="n"/>
+      <c r="Q24" s="246" t="n"/>
+      <c r="R24" s="246" t="n"/>
+      <c r="S24" s="246" t="n"/>
+      <c r="T24" s="246" t="n"/>
+      <c r="U24" s="246" t="n"/>
+      <c r="V24" s="246" t="n"/>
+      <c r="W24" s="246" t="n"/>
+      <c r="X24" s="246" t="n"/>
+      <c r="Y24" s="246" t="n"/>
+      <c r="Z24" s="246" t="n"/>
+      <c r="AA24" s="246" t="n"/>
+      <c r="AB24" s="246" t="n"/>
+      <c r="AC24" s="246" t="n"/>
+      <c r="AD24" s="246" t="n"/>
+      <c r="AE24" s="246" t="n"/>
+      <c r="AF24" s="246" t="n"/>
+      <c r="AG24" s="246" t="n"/>
       <c r="AH24" s="244" t="inlineStr">
         <is>
           <t>6Б,6В
@@ -12294,12 +12311,12 @@
 каб. робототехники (№15)</t>
         </is>
       </c>
-      <c r="AJ24" s="245" t="n"/>
-      <c r="AK24" s="245" t="n"/>
-      <c r="AL24" s="245" t="n"/>
-      <c r="AM24" s="245" t="n"/>
-      <c r="AN24" s="245" t="n"/>
-      <c r="AO24" s="245" t="n"/>
+      <c r="AJ24" s="246" t="n"/>
+      <c r="AK24" s="246" t="n"/>
+      <c r="AL24" s="246" t="n"/>
+      <c r="AM24" s="246" t="n"/>
+      <c r="AN24" s="246" t="n"/>
+      <c r="AO24" s="246" t="n"/>
       <c r="AP24" s="243" t="n">
         <v>4</v>
       </c>
@@ -12331,7 +12348,7 @@
 каб. мультимедийный (№18)</t>
         </is>
       </c>
-      <c r="E25" s="246" t="inlineStr">
+      <c r="E25" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -12428,7 +12445,7 @@
 каб. мультимедийный (№18)</t>
         </is>
       </c>
-      <c r="AB25" s="246" t="inlineStr">
+      <c r="AB25" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -12512,7 +12529,7 @@
 малый зал</t>
         </is>
       </c>
-      <c r="E26" s="246" t="inlineStr">
+      <c r="E26" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -12577,7 +12594,7 @@
 малый зал</t>
         </is>
       </c>
-      <c r="AJ26" s="246" t="inlineStr">
+      <c r="AJ26" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -12667,7 +12684,7 @@
 нач. класс 2Б (№6)</t>
         </is>
       </c>
-      <c r="S27" s="245" t="n"/>
+      <c r="S27" s="246" t="n"/>
       <c r="T27" s="244" t="inlineStr">
         <is>
           <t>2Б
@@ -12784,12 +12801,12 @@
 каб. биологии (№19)</t>
         </is>
       </c>
-      <c r="M28" s="246" t="inlineStr">
+      <c r="M28" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="N28" s="246" t="inlineStr">
+      <c r="N28" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -12819,14 +12836,14 @@
 каб. химии (№17)</t>
         </is>
       </c>
-      <c r="T28" s="245" t="n"/>
+      <c r="T28" s="246" t="n"/>
       <c r="U28" s="244" t="inlineStr">
         <is>
           <t>10А
 каб. биологии (№19)</t>
         </is>
       </c>
-      <c r="V28" s="246" t="inlineStr">
+      <c r="V28" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -12857,12 +12874,12 @@
 каб. биологии (№19)</t>
         </is>
       </c>
-      <c r="AC28" s="246" t="inlineStr">
+      <c r="AC28" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="AD28" s="246" t="inlineStr">
+      <c r="AD28" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -12887,7 +12904,7 @@
 каб. биологии (№19)</t>
         </is>
       </c>
-      <c r="AJ28" s="246" t="inlineStr">
+      <c r="AJ28" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -12935,9 +12952,9 @@
       <c r="D29" s="244" t="n"/>
       <c r="E29" s="244" t="n"/>
       <c r="F29" s="244" t="n"/>
-      <c r="G29" s="245" t="n"/>
-      <c r="H29" s="245" t="n"/>
-      <c r="I29" s="245" t="n"/>
+      <c r="G29" s="246" t="n"/>
+      <c r="H29" s="246" t="n"/>
+      <c r="I29" s="246" t="n"/>
       <c r="J29" s="244" t="n"/>
       <c r="K29" s="244" t="inlineStr">
         <is>
@@ -12945,12 +12962,12 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="L29" s="246" t="inlineStr">
+      <c r="L29" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="M29" s="246" t="inlineStr">
+      <c r="M29" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -12961,9 +12978,9 @@
 малый зал</t>
         </is>
       </c>
-      <c r="O29" s="245" t="n"/>
-      <c r="P29" s="245" t="n"/>
-      <c r="Q29" s="245" t="n"/>
+      <c r="O29" s="246" t="n"/>
+      <c r="P29" s="246" t="n"/>
+      <c r="Q29" s="246" t="n"/>
       <c r="R29" s="244" t="n"/>
       <c r="S29" s="244" t="n"/>
       <c r="T29" s="244" t="n"/>
@@ -12974,9 +12991,9 @@
 малый зал</t>
         </is>
       </c>
-      <c r="W29" s="245" t="n"/>
-      <c r="X29" s="245" t="n"/>
-      <c r="Y29" s="245" t="n"/>
+      <c r="W29" s="246" t="n"/>
+      <c r="X29" s="246" t="n"/>
+      <c r="Y29" s="246" t="n"/>
       <c r="Z29" s="244" t="n"/>
       <c r="AA29" s="244" t="inlineStr">
         <is>
@@ -12984,7 +13001,7 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="AB29" s="246" t="inlineStr">
+      <c r="AB29" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -13001,9 +13018,9 @@
 малый зал</t>
         </is>
       </c>
-      <c r="AE29" s="245" t="n"/>
-      <c r="AF29" s="245" t="n"/>
-      <c r="AG29" s="245" t="n"/>
+      <c r="AE29" s="246" t="n"/>
+      <c r="AF29" s="246" t="n"/>
+      <c r="AG29" s="246" t="n"/>
       <c r="AH29" s="244" t="inlineStr">
         <is>
           <t>10А
@@ -13014,9 +13031,9 @@
       <c r="AJ29" s="244" t="n"/>
       <c r="AK29" s="244" t="n"/>
       <c r="AL29" s="244" t="n"/>
-      <c r="AM29" s="245" t="n"/>
-      <c r="AN29" s="245" t="n"/>
-      <c r="AO29" s="245" t="n"/>
+      <c r="AM29" s="246" t="n"/>
+      <c r="AN29" s="246" t="n"/>
+      <c r="AO29" s="246" t="n"/>
       <c r="AP29" s="243" t="n">
         <v>9</v>
       </c>
@@ -13040,17 +13057,17 @@
         </is>
       </c>
       <c r="F30" s="244" t="n"/>
-      <c r="G30" s="245" t="n"/>
-      <c r="H30" s="245" t="n"/>
-      <c r="I30" s="245" t="n"/>
+      <c r="G30" s="246" t="n"/>
+      <c r="H30" s="246" t="n"/>
+      <c r="I30" s="246" t="n"/>
       <c r="J30" s="244" t="n"/>
       <c r="K30" s="244" t="n"/>
-      <c r="L30" s="245" t="n"/>
+      <c r="L30" s="246" t="n"/>
       <c r="M30" s="244" t="n"/>
       <c r="N30" s="244" t="n"/>
-      <c r="O30" s="245" t="n"/>
-      <c r="P30" s="245" t="n"/>
-      <c r="Q30" s="245" t="n"/>
+      <c r="O30" s="246" t="n"/>
+      <c r="P30" s="246" t="n"/>
+      <c r="Q30" s="246" t="n"/>
       <c r="R30" s="244" t="n"/>
       <c r="S30" s="244" t="n"/>
       <c r="T30" s="244" t="n"/>
@@ -13061,25 +13078,25 @@
 каб. истории (№14)</t>
         </is>
       </c>
-      <c r="W30" s="245" t="n"/>
-      <c r="X30" s="245" t="n"/>
-      <c r="Y30" s="245" t="n"/>
+      <c r="W30" s="246" t="n"/>
+      <c r="X30" s="246" t="n"/>
+      <c r="Y30" s="246" t="n"/>
       <c r="Z30" s="244" t="n"/>
       <c r="AA30" s="244" t="n"/>
-      <c r="AB30" s="245" t="n"/>
+      <c r="AB30" s="246" t="n"/>
       <c r="AC30" s="244" t="n"/>
       <c r="AD30" s="244" t="inlineStr">
         <is>
           <t>6Б
-каб. истории (№14)</t>
-        </is>
-      </c>
-      <c r="AE30" s="245" t="n"/>
-      <c r="AF30" s="245" t="n"/>
-      <c r="AG30" s="245" t="n"/>
+каб. робототехники (№15)</t>
+        </is>
+      </c>
+      <c r="AE30" s="246" t="n"/>
+      <c r="AF30" s="246" t="n"/>
+      <c r="AG30" s="246" t="n"/>
       <c r="AH30" s="244" t="n"/>
       <c r="AI30" s="244" t="n"/>
-      <c r="AJ30" s="245" t="n"/>
+      <c r="AJ30" s="246" t="n"/>
       <c r="AK30" s="244" t="inlineStr">
         <is>
           <t>7А
@@ -13092,9 +13109,9 @@
 каб. математики (№25)</t>
         </is>
       </c>
-      <c r="AM30" s="245" t="n"/>
-      <c r="AN30" s="245" t="n"/>
-      <c r="AO30" s="245" t="n"/>
+      <c r="AM30" s="246" t="n"/>
+      <c r="AN30" s="246" t="n"/>
+      <c r="AO30" s="246" t="n"/>
       <c r="AP30" s="243" t="n">
         <v>5</v>
       </c>
@@ -13117,7 +13134,7 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="F31" s="246" t="inlineStr">
+      <c r="F31" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -13144,7 +13161,7 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="N31" s="246" t="inlineStr">
+      <c r="N31" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -13168,19 +13185,20 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="S31" s="246" t="inlineStr">
+      <c r="S31" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="T31" s="246" t="inlineStr">
+      <c r="T31" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="U31" s="246" t="inlineStr">
-        <is>
-          <t>окно</t>
+      <c r="U31" s="244" t="inlineStr">
+        <is>
+          <t>7А
+спортзал (№01)</t>
         </is>
       </c>
       <c r="V31" s="244" t="inlineStr">
@@ -13189,10 +13207,9 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="W31" s="244" t="inlineStr">
-        <is>
-          <t>7А
-спортзал (№01)</t>
+      <c r="W31" s="245" t="inlineStr">
+        <is>
+          <t>окно</t>
         </is>
       </c>
       <c r="X31" s="244" t="inlineStr">
@@ -13208,22 +13225,22 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="AA31" s="246" t="inlineStr">
+      <c r="AA31" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="AB31" s="246" t="inlineStr">
+      <c r="AB31" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="AC31" s="246" t="inlineStr">
+      <c r="AC31" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="AD31" s="246" t="inlineStr">
+      <c r="AD31" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -13250,7 +13267,7 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="AL31" s="246" t="inlineStr">
+      <c r="AL31" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -13288,14 +13305,14 @@
 каб. математики (№25)</t>
         </is>
       </c>
-      <c r="D32" s="245" t="n"/>
+      <c r="D32" s="246" t="n"/>
       <c r="E32" s="244" t="n"/>
       <c r="F32" s="244" t="n"/>
       <c r="G32" s="244" t="n"/>
       <c r="H32" s="244" t="n"/>
       <c r="I32" s="244" t="n"/>
       <c r="J32" s="244" t="n"/>
-      <c r="K32" s="245" t="n"/>
+      <c r="K32" s="246" t="n"/>
       <c r="L32" s="244" t="inlineStr">
         <is>
           <t>6Б,6В
@@ -13406,7 +13423,7 @@
 нач. класс 4Б (№9)</t>
         </is>
       </c>
-      <c r="D33" s="246" t="inlineStr">
+      <c r="D33" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -13439,7 +13456,7 @@
 нач. класс 4Б (№9)</t>
         </is>
       </c>
-      <c r="M33" s="246" t="inlineStr">
+      <c r="M33" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -13465,12 +13482,12 @@
 нач. класс 4Б (№9)</t>
         </is>
       </c>
-      <c r="T33" s="246" t="inlineStr">
+      <c r="T33" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="U33" s="246" t="inlineStr">
+      <c r="U33" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -13502,7 +13519,7 @@
 нач. класс 4Б (№9)</t>
         </is>
       </c>
-      <c r="AC33" s="246" t="inlineStr">
+      <c r="AC33" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -13602,22 +13619,18 @@
 каб. физики (№16)</t>
         </is>
       </c>
-      <c r="V34" s="246" t="inlineStr">
+      <c r="V34" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="W34" s="246" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="X34" s="244" t="inlineStr">
+      <c r="W34" s="244" t="inlineStr">
         <is>
           <t>7А
 каб. физики (№16)</t>
         </is>
       </c>
+      <c r="X34" s="244" t="n"/>
       <c r="Y34" s="244" t="n"/>
       <c r="Z34" s="244" t="n"/>
       <c r="AA34" s="244" t="n"/>
@@ -13632,43 +13645,39 @@
       <c r="AE34" s="244" t="n"/>
       <c r="AF34" s="244" t="n"/>
       <c r="AG34" s="244" t="n"/>
-      <c r="AH34" s="244" t="inlineStr">
+      <c r="AH34" s="244" t="n"/>
+      <c r="AI34" s="244" t="n"/>
+      <c r="AJ34" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+каб. физики (№16)</t>
+        </is>
+      </c>
+      <c r="AK34" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+каб. физики (№16)</t>
+        </is>
+      </c>
+      <c r="AL34" s="244" t="inlineStr">
+        <is>
+          <t>10А
+каб. физики (№16)</t>
+        </is>
+      </c>
+      <c r="AM34" s="244" t="inlineStr">
         <is>
           <t>7А
 каб. физики (№16)</t>
         </is>
       </c>
-      <c r="AI34" s="246" t="inlineStr">
-        <is>
-          <t>окно</t>
-        </is>
-      </c>
-      <c r="AJ34" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-каб. физики (№16)</t>
-        </is>
-      </c>
-      <c r="AK34" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-каб. физики (№16)</t>
-        </is>
-      </c>
-      <c r="AL34" s="244" t="inlineStr">
-        <is>
-          <t>10А
-каб. физики (№16)</t>
-        </is>
-      </c>
-      <c r="AM34" s="244" t="n"/>
       <c r="AN34" s="244" t="n"/>
       <c r="AO34" s="244" t="n"/>
       <c r="AP34" s="243" t="n">
         <v>13</v>
       </c>
       <c r="AQ34" s="243" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
@@ -13677,25 +13686,25 @@
           <t>Сапаргалиева Г.С.</t>
         </is>
       </c>
-      <c r="B35" s="245" t="n"/>
-      <c r="C35" s="245" t="n"/>
-      <c r="D35" s="245" t="n"/>
-      <c r="E35" s="245" t="n"/>
-      <c r="F35" s="245" t="n"/>
-      <c r="G35" s="245" t="n"/>
-      <c r="H35" s="245" t="n"/>
-      <c r="I35" s="245" t="n"/>
-      <c r="J35" s="245" t="n"/>
-      <c r="K35" s="245" t="n"/>
-      <c r="L35" s="245" t="n"/>
-      <c r="M35" s="245" t="n"/>
-      <c r="N35" s="245" t="n"/>
-      <c r="O35" s="245" t="n"/>
-      <c r="P35" s="245" t="n"/>
-      <c r="Q35" s="245" t="n"/>
-      <c r="R35" s="245" t="n"/>
-      <c r="S35" s="245" t="n"/>
-      <c r="T35" s="245" t="n"/>
+      <c r="B35" s="246" t="n"/>
+      <c r="C35" s="246" t="n"/>
+      <c r="D35" s="246" t="n"/>
+      <c r="E35" s="246" t="n"/>
+      <c r="F35" s="246" t="n"/>
+      <c r="G35" s="246" t="n"/>
+      <c r="H35" s="246" t="n"/>
+      <c r="I35" s="246" t="n"/>
+      <c r="J35" s="246" t="n"/>
+      <c r="K35" s="246" t="n"/>
+      <c r="L35" s="246" t="n"/>
+      <c r="M35" s="246" t="n"/>
+      <c r="N35" s="246" t="n"/>
+      <c r="O35" s="246" t="n"/>
+      <c r="P35" s="246" t="n"/>
+      <c r="Q35" s="246" t="n"/>
+      <c r="R35" s="246" t="n"/>
+      <c r="S35" s="246" t="n"/>
+      <c r="T35" s="246" t="n"/>
       <c r="U35" s="244" t="inlineStr">
         <is>
           <t>5А
@@ -13721,9 +13730,9 @@
         </is>
       </c>
       <c r="Y35" s="244" t="n"/>
-      <c r="Z35" s="245" t="n"/>
-      <c r="AA35" s="245" t="n"/>
-      <c r="AB35" s="245" t="n"/>
+      <c r="Z35" s="246" t="n"/>
+      <c r="AA35" s="246" t="n"/>
+      <c r="AB35" s="246" t="n"/>
       <c r="AC35" s="244" t="inlineStr">
         <is>
           <t>6А
@@ -13749,14 +13758,14 @@
         </is>
       </c>
       <c r="AG35" s="244" t="n"/>
-      <c r="AH35" s="245" t="n"/>
-      <c r="AI35" s="245" t="n"/>
-      <c r="AJ35" s="245" t="n"/>
-      <c r="AK35" s="245" t="n"/>
-      <c r="AL35" s="245" t="n"/>
-      <c r="AM35" s="245" t="n"/>
-      <c r="AN35" s="245" t="n"/>
-      <c r="AO35" s="245" t="n"/>
+      <c r="AH35" s="246" t="n"/>
+      <c r="AI35" s="246" t="n"/>
+      <c r="AJ35" s="246" t="n"/>
+      <c r="AK35" s="246" t="n"/>
+      <c r="AL35" s="246" t="n"/>
+      <c r="AM35" s="246" t="n"/>
+      <c r="AN35" s="246" t="n"/>
+      <c r="AO35" s="246" t="n"/>
       <c r="AP35" s="243" t="n">
         <v>8</v>
       </c>
@@ -13770,26 +13779,26 @@
           <t>Сидоров В.Б.</t>
         </is>
       </c>
-      <c r="B36" s="245" t="n"/>
-      <c r="C36" s="245" t="n"/>
-      <c r="D36" s="245" t="n"/>
-      <c r="E36" s="245" t="n"/>
-      <c r="F36" s="245" t="n"/>
-      <c r="G36" s="245" t="n"/>
-      <c r="H36" s="245" t="n"/>
-      <c r="I36" s="245" t="n"/>
+      <c r="B36" s="246" t="n"/>
+      <c r="C36" s="246" t="n"/>
+      <c r="D36" s="246" t="n"/>
+      <c r="E36" s="246" t="n"/>
+      <c r="F36" s="246" t="n"/>
+      <c r="G36" s="246" t="n"/>
+      <c r="H36" s="246" t="n"/>
+      <c r="I36" s="246" t="n"/>
       <c r="J36" s="244" t="inlineStr">
         <is>
           <t>7А
 каб. НВП (№28)</t>
         </is>
       </c>
-      <c r="K36" s="246" t="inlineStr">
+      <c r="K36" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="L36" s="246" t="inlineStr">
+      <c r="L36" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -13819,14 +13828,14 @@
         </is>
       </c>
       <c r="Q36" s="244" t="n"/>
-      <c r="R36" s="245" t="n"/>
-      <c r="S36" s="245" t="n"/>
-      <c r="T36" s="245" t="n"/>
-      <c r="U36" s="245" t="n"/>
-      <c r="V36" s="245" t="n"/>
-      <c r="W36" s="245" t="n"/>
-      <c r="X36" s="245" t="n"/>
-      <c r="Y36" s="245" t="n"/>
+      <c r="R36" s="246" t="n"/>
+      <c r="S36" s="246" t="n"/>
+      <c r="T36" s="246" t="n"/>
+      <c r="U36" s="246" t="n"/>
+      <c r="V36" s="246" t="n"/>
+      <c r="W36" s="246" t="n"/>
+      <c r="X36" s="246" t="n"/>
+      <c r="Y36" s="246" t="n"/>
       <c r="Z36" s="244" t="n"/>
       <c r="AA36" s="244" t="n"/>
       <c r="AB36" s="244" t="inlineStr">
@@ -13860,14 +13869,14 @@
         </is>
       </c>
       <c r="AG36" s="244" t="n"/>
-      <c r="AH36" s="245" t="n"/>
-      <c r="AI36" s="245" t="n"/>
-      <c r="AJ36" s="245" t="n"/>
-      <c r="AK36" s="245" t="n"/>
-      <c r="AL36" s="245" t="n"/>
-      <c r="AM36" s="245" t="n"/>
-      <c r="AN36" s="245" t="n"/>
-      <c r="AO36" s="245" t="n"/>
+      <c r="AH36" s="246" t="n"/>
+      <c r="AI36" s="246" t="n"/>
+      <c r="AJ36" s="246" t="n"/>
+      <c r="AK36" s="246" t="n"/>
+      <c r="AL36" s="246" t="n"/>
+      <c r="AM36" s="246" t="n"/>
+      <c r="AN36" s="246" t="n"/>
+      <c r="AO36" s="246" t="n"/>
       <c r="AP36" s="243" t="n">
         <v>10</v>
       </c>
@@ -13896,7 +13905,7 @@
       <c r="D37" s="244" t="inlineStr">
         <is>
           <t>6Б,6В
-каб. технологии (мальчики) (№39)</t>
+каб. математики (№25)</t>
         </is>
       </c>
       <c r="E37" s="244" t="inlineStr">
@@ -13936,7 +13945,7 @@
       <c r="N37" s="244" t="inlineStr">
         <is>
           <t>6Б,6В
-каб. технологии (мальчики) (№39)</t>
+каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="O37" s="244" t="n"/>
@@ -13957,7 +13966,7 @@
       <c r="T37" s="244" t="inlineStr">
         <is>
           <t>6Б,6В
-каб. технологии (мальчики) (№39)</t>
+каб. биологии (№19)</t>
         </is>
       </c>
       <c r="U37" s="244" t="inlineStr">
@@ -13991,7 +14000,7 @@
       <c r="AC37" s="244" t="inlineStr">
         <is>
           <t>6Б,6В
-каб. технологии (мальчики) (№39)</t>
+каб. истории (№14)</t>
         </is>
       </c>
       <c r="AD37" s="244" t="inlineStr">
@@ -14015,7 +14024,7 @@
 нач. класс 3А (№7)</t>
         </is>
       </c>
-      <c r="AJ37" s="246" t="inlineStr">
+      <c r="AJ37" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -14023,7 +14032,7 @@
       <c r="AK37" s="244" t="inlineStr">
         <is>
           <t>6Б,6В
-каб. технологии (мальчики) (№39)</t>
+каб. английского языка (№27)</t>
         </is>
       </c>
       <c r="AL37" s="244" t="n"/>
@@ -14097,12 +14106,12 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="U38" s="246" t="inlineStr">
+      <c r="U38" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
       </c>
-      <c r="V38" s="246" t="inlineStr">
+      <c r="V38" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -14141,7 +14150,7 @@
 спортзал (№01)</t>
         </is>
       </c>
-      <c r="AK38" s="246" t="inlineStr">
+      <c r="AK38" s="245" t="inlineStr">
         <is>
           <t>окно</t>
         </is>
@@ -14579,7 +14588,7 @@
       <c r="G4" s="244" t="inlineStr">
         <is>
           <t>8Ә
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="J4" s="244" t="inlineStr">
@@ -14645,13 +14654,13 @@
       <c r="Z4" s="244" t="inlineStr">
         <is>
           <t>8Ә
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="AA4" s="244" t="inlineStr">
         <is>
           <t>7А
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="AB4" s="244" t="inlineStr">
@@ -14730,7 +14739,7 @@
       <c r="B5" s="244" t="inlineStr">
         <is>
           <t>8А
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="C5" s="244" t="inlineStr">
@@ -14787,6 +14796,12 @@
 Акауова</t>
         </is>
       </c>
+      <c r="N5" s="244" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Темерканова</t>
+        </is>
+      </c>
       <c r="R5" s="244" t="inlineStr">
         <is>
           <t>4А
@@ -14802,7 +14817,7 @@
       <c r="T5" s="244" t="inlineStr">
         <is>
           <t>8А
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="U5" s="244" t="inlineStr">
@@ -14814,13 +14829,13 @@
       <c r="V5" s="244" t="inlineStr">
         <is>
           <t>7А
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="W5" s="244" t="inlineStr">
         <is>
           <t>8Ә
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="X5" s="244" t="inlineStr">
@@ -14850,7 +14865,7 @@
       <c r="AD5" s="244" t="inlineStr">
         <is>
           <t>8А
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="AE5" s="244" t="inlineStr">
@@ -14868,13 +14883,13 @@
       <c r="AH5" s="244" t="inlineStr">
         <is>
           <t>8Ә
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="AI5" s="244" t="inlineStr">
         <is>
           <t>7А
-Дюсембаева</t>
+Власова</t>
         </is>
       </c>
       <c r="AJ5" s="244" t="inlineStr">
@@ -14883,6 +14898,12 @@
 Акауова</t>
         </is>
       </c>
+      <c r="AK5" s="244" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Темерканова</t>
+        </is>
+      </c>
       <c r="AM5" s="244" t="inlineStr">
         <is>
           <t>6Б
@@ -14962,6 +14983,12 @@
 Бабич</t>
         </is>
       </c>
+      <c r="T6" s="244" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Темерканова</t>
+        </is>
+      </c>
       <c r="U6" s="244" t="inlineStr">
         <is>
           <t>10А
@@ -15336,2470 +15363,2470 @@
 Досаева</t>
         </is>
       </c>
+      <c r="AC8" s="244" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Темерканова</t>
+        </is>
+      </c>
       <c r="AD8" s="244" t="inlineStr">
+        <is>
+          <t>8Ә
+Досаева</t>
+        </is>
+      </c>
+      <c r="AE8" s="244" t="inlineStr">
+        <is>
+          <t>8Ә
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="AH8" s="244" t="inlineStr">
+        <is>
+          <t>11А
+Досаева</t>
+        </is>
+      </c>
+      <c r="AK8" s="244" t="inlineStr">
+        <is>
+          <t>8Ә
+Досаева</t>
+        </is>
+      </c>
+      <c r="AL8" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+Досаева</t>
+        </is>
+      </c>
+      <c r="AM8" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Досаева</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="248" t="inlineStr">
+        <is>
+          <t>Кабинет казахского языка (№24)</t>
+        </is>
+      </c>
+      <c r="B9" s="244" t="inlineStr">
+        <is>
+          <t>6А
+Асаева</t>
+        </is>
+      </c>
+      <c r="C9" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="D9" s="244" t="inlineStr">
+        <is>
+          <t>8Ә
+Балташева</t>
+        </is>
+      </c>
+      <c r="E9" s="244" t="inlineStr">
+        <is>
+          <t>8Ә
+Балташева</t>
+        </is>
+      </c>
+      <c r="G9" s="244" t="inlineStr">
+        <is>
+          <t>11А
+Балташева</t>
+        </is>
+      </c>
+      <c r="J9" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="K9" s="244" t="inlineStr">
+        <is>
+          <t>6А
+Асаева</t>
+        </is>
+      </c>
+      <c r="L9" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="N9" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="R9" s="244" t="inlineStr">
+        <is>
+          <t>6А
+Асаева</t>
+        </is>
+      </c>
+      <c r="S9" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="T9" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="U9" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="V9" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="W9" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="Z9" s="244" t="inlineStr">
+        <is>
+          <t>6А
+Асаева</t>
+        </is>
+      </c>
+      <c r="AB9" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="AC9" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AD9" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="AE9" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="AH9" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AI9" s="244" t="inlineStr">
+        <is>
+          <t>6А
+Асаева</t>
+        </is>
+      </c>
+      <c r="AJ9" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AK9" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="AL9" s="244" t="inlineStr">
+        <is>
+          <t>6Б
+Алекпарова</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="248" t="inlineStr">
+        <is>
+          <t>Кабинет казахского языка и литературы (№23)</t>
+        </is>
+      </c>
+      <c r="B10" s="244" t="inlineStr">
+        <is>
+          <t>2А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="C10" s="244" t="inlineStr">
+        <is>
+          <t>8Ә
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="D10" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="E10" s="244" t="inlineStr">
+        <is>
+          <t>6А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="F10" s="244" t="inlineStr">
+        <is>
+          <t>6Б
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="J10" s="244" t="inlineStr">
+        <is>
+          <t>8Ә
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="K10" s="244" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="L10" s="244" t="inlineStr">
+        <is>
+          <t>6А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="M10" s="244" t="inlineStr">
+        <is>
+          <t>4А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="N10" s="244" t="inlineStr">
+        <is>
+          <t>5А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="O10" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="R10" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="S10" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="T10" s="244" t="inlineStr">
+        <is>
+          <t>5А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="U10" s="244" t="inlineStr">
+        <is>
+          <t>6Б
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="W10" s="244" t="inlineStr">
+        <is>
+          <t>11А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="Z10" s="244" t="inlineStr">
+        <is>
+          <t>2А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="AA10" s="244" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="AB10" s="244" t="inlineStr">
+        <is>
+          <t>8Ә
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="AC10" s="244" t="inlineStr">
+        <is>
+          <t>5А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="AD10" s="244" t="inlineStr">
+        <is>
+          <t>6А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="AE10" s="244" t="inlineStr">
+        <is>
+          <t>6Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AF10" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AH10" s="244" t="inlineStr">
+        <is>
+          <t>4А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="AI10" s="244" t="inlineStr">
+        <is>
+          <t>8Ә
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AK10" s="244" t="inlineStr">
+        <is>
+          <t>11А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="AL10" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Балгабаева</t>
+        </is>
+      </c>
+      <c r="AM10" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Балгабаева</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="248" t="inlineStr">
+        <is>
+          <t>Кабинет математики (№25)</t>
+        </is>
+      </c>
+      <c r="B11" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+Пащенко</t>
+        </is>
+      </c>
+      <c r="C11" s="244" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Пащенко</t>
+        </is>
+      </c>
+      <c r="D11" s="244" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Темерканова</t>
+        </is>
+      </c>
+      <c r="E11" s="244" t="inlineStr">
         <is>
           <t>6Б
 Мельникова</t>
         </is>
       </c>
-      <c r="AE8" s="244" t="inlineStr">
+      <c r="F11" s="244" t="inlineStr">
+        <is>
+          <t>2А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="K11" s="244" t="inlineStr">
+        <is>
+          <t>2А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="L11" s="244" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Пащенко</t>
+        </is>
+      </c>
+      <c r="M11" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+Пащенко</t>
+        </is>
+      </c>
+      <c r="N11" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Пащенко</t>
+        </is>
+      </c>
+      <c r="R11" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+Пащенко</t>
+        </is>
+      </c>
+      <c r="S11" s="244" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Пащенко</t>
+        </is>
+      </c>
+      <c r="T11" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Пащенко</t>
+        </is>
+      </c>
+      <c r="U11" s="244" t="inlineStr">
+        <is>
+          <t>5А
+Сапаргалиева</t>
+        </is>
+      </c>
+      <c r="V11" s="244" t="inlineStr">
+        <is>
+          <t>11А
+Сапаргалиева</t>
+        </is>
+      </c>
+      <c r="W11" s="244" t="inlineStr">
+        <is>
+          <t>6А
+Сапаргалиева</t>
+        </is>
+      </c>
+      <c r="X11" s="244" t="inlineStr">
         <is>
           <t>8Ә
-Досаева</t>
-        </is>
-      </c>
-      <c r="AH8" s="244" t="inlineStr">
+Сапаргалиева</t>
+        </is>
+      </c>
+      <c r="AA11" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+Пащенко</t>
+        </is>
+      </c>
+      <c r="AB11" s="244" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Пащенко</t>
+        </is>
+      </c>
+      <c r="AC11" s="244" t="inlineStr">
+        <is>
+          <t>6А
+Сапаргалиева</t>
+        </is>
+      </c>
+      <c r="AD11" s="244" t="inlineStr">
+        <is>
+          <t>5А
+Сапаргалиева</t>
+        </is>
+      </c>
+      <c r="AE11" s="244" t="inlineStr">
         <is>
           <t>11А
-Досаева</t>
-        </is>
-      </c>
-      <c r="AK8" s="244" t="inlineStr">
+Сапаргалиева</t>
+        </is>
+      </c>
+      <c r="AF11" s="244" t="inlineStr">
         <is>
           <t>8Ә
-Досаева</t>
-        </is>
-      </c>
-      <c r="AL8" s="244" t="inlineStr">
+Сапаргалиева</t>
+        </is>
+      </c>
+      <c r="AH11" s="244" t="inlineStr">
         <is>
           <t>11Б
-Досаева</t>
-        </is>
-      </c>
-      <c r="AM8" s="244" t="inlineStr">
+Пащенко</t>
+        </is>
+      </c>
+      <c r="AI11" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+Пащенко</t>
+        </is>
+      </c>
+      <c r="AJ11" s="244" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Пащенко</t>
+        </is>
+      </c>
+      <c r="AK11" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Мельникова</t>
+        </is>
+      </c>
+      <c r="AL11" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Мельникова</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="248" t="inlineStr">
+        <is>
+          <t>Кабинет мультимедийный (№18)</t>
+        </is>
+      </c>
+      <c r="B12" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="C12" s="244" t="inlineStr">
+        <is>
+          <t>11А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="D12" s="244" t="inlineStr">
+        <is>
+          <t>5А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="E12" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="F12" s="244" t="inlineStr">
+        <is>
+          <t>6Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="J12" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="K12" s="244" t="inlineStr">
+        <is>
+          <t>6Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="L12" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="M12" s="244" t="inlineStr">
+        <is>
+          <t>5А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="N12" s="244" t="inlineStr">
         <is>
           <t>9Б
-Досаева</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="248" t="inlineStr">
-        <is>
-          <t>Кабинет казахского языка (№24)</t>
-        </is>
-      </c>
-      <c r="B9" s="244" t="inlineStr">
+Ильясова</t>
+        </is>
+      </c>
+      <c r="O12" s="244" t="inlineStr">
+        <is>
+          <t>11А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="R12" s="244" t="inlineStr">
+        <is>
+          <t>5А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="S12" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="T12" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="U12" s="244" t="inlineStr">
+        <is>
+          <t>6Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="V12" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="Z12" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="AA12" s="244" t="inlineStr">
+        <is>
+          <t>6Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="AC12" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="AD12" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Ильясова</t>
+        </is>
+      </c>
+      <c r="AE12" s="244" t="inlineStr">
+        <is>
+          <t>5А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="AH12" s="244" t="inlineStr">
+        <is>
+          <t>5А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="AI12" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="AJ12" s="244" t="inlineStr">
+        <is>
+          <t>11А
+Ильясова</t>
+        </is>
+      </c>
+      <c r="AK12" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Ильясова</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1">
+      <c r="A13" s="248" t="inlineStr">
+        <is>
+          <t>Кабинет робототехники (№15)</t>
+        </is>
+      </c>
+      <c r="B13" s="244" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Иващенко</t>
+        </is>
+      </c>
+      <c r="C13" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Иващенко</t>
+        </is>
+      </c>
+      <c r="E13" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Бучкова</t>
+        </is>
+      </c>
+      <c r="G13" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Бучкова</t>
+        </is>
+      </c>
+      <c r="J13" s="244" t="inlineStr">
+        <is>
+          <t>11А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="K13" s="244" t="inlineStr">
+        <is>
+          <t>8Ә
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="L13" s="244" t="inlineStr">
+        <is>
+          <t>5А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="M13" s="244" t="inlineStr">
         <is>
           <t>6А
-Асаева</t>
-        </is>
-      </c>
-      <c r="C9" s="244" t="inlineStr">
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="N13" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Бучкова</t>
+        </is>
+      </c>
+      <c r="O13" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Бучкова</t>
+        </is>
+      </c>
+      <c r="R13" s="244" t="inlineStr">
+        <is>
+          <t>11А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="S13" s="244" t="inlineStr">
+        <is>
+          <t>5А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="T13" s="244" t="inlineStr">
+        <is>
+          <t>6А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="U13" s="244" t="inlineStr">
+        <is>
+          <t>8Ә
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="V13" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Бучкова</t>
+        </is>
+      </c>
+      <c r="W13" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Бучкова</t>
+        </is>
+      </c>
+      <c r="Z13" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AA13" s="244" t="inlineStr">
+        <is>
+          <t>8Ә
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AB13" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="AC13" s="244" t="inlineStr">
+        <is>
+          <t>11А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="AD13" s="244" t="inlineStr">
+        <is>
+          <t>6Б
+Мельникова</t>
+        </is>
+      </c>
+      <c r="AE13" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Бучкова</t>
+        </is>
+      </c>
+      <c r="AH13" s="244" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Иващенко</t>
+        </is>
+      </c>
+      <c r="AI13" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Иващенко</t>
+        </is>
+      </c>
+      <c r="AK13" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Бучкова</t>
+        </is>
+      </c>
+      <c r="AL13" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Бучкова</t>
+        </is>
+      </c>
+      <c r="AM13" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Бучкова</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="248" t="inlineStr">
+        <is>
+          <t>Кабинет русского языка (№20)</t>
+        </is>
+      </c>
+      <c r="B14" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="C14" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="D14" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="E14" s="244" t="inlineStr">
         <is>
           <t>8Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="D9" s="244" t="inlineStr">
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="F14" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="L14" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="M14" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="N14" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="P14" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="R14" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="S14" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="T14" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="U14" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="V14" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="W14" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="Z14" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="AA14" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="AB14" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="AC14" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="AD14" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="AH14" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="AI14" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="AJ14" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Дмитриев</t>
+        </is>
+      </c>
+      <c r="AK14" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Дмитриев</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="248" t="inlineStr">
+        <is>
+          <t>Кабинет технологии (девочки) (№29)</t>
+        </is>
+      </c>
+      <c r="C15" s="244" t="inlineStr">
+        <is>
+          <t>2А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="D15" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="E15" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="F15" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="G15" s="244" t="inlineStr">
+        <is>
+          <t>6Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="J15" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="K15" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="L15" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="N15" s="244" t="inlineStr">
         <is>
           <t>8Ә
-Балташева</t>
-        </is>
-      </c>
-      <c r="E9" s="244" t="inlineStr">
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="O15" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="S15" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Жукова</t>
+        </is>
+      </c>
+      <c r="T15" s="244" t="inlineStr">
+        <is>
+          <t>2А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="V15" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="W15" s="244" t="inlineStr">
+        <is>
+          <t>6Б
+Жукова</t>
+        </is>
+      </c>
+      <c r="AA15" s="244" t="inlineStr">
+        <is>
+          <t>2А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="AB15" s="244" t="inlineStr">
+        <is>
+          <t>2А,4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="AC15" s="244" t="inlineStr">
+        <is>
+          <t>2А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="AD15" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Жукова</t>
+        </is>
+      </c>
+      <c r="AF15" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Жукова</t>
+        </is>
+      </c>
+      <c r="AH15" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Жукова</t>
+        </is>
+      </c>
+      <c r="AI15" s="244" t="inlineStr">
+        <is>
+          <t>6Б,6В
+Жукова</t>
+        </is>
+      </c>
+      <c r="AJ15" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Жукова</t>
+        </is>
+      </c>
+      <c r="AK15" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="AL15" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Жукова</t>
+        </is>
+      </c>
+      <c r="AM15" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Жукова</t>
+        </is>
+      </c>
+      <c r="AN15" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Жукова</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="248" t="inlineStr">
+        <is>
+          <t>Кабинет технологии (мальчики) (№39)</t>
+        </is>
+      </c>
+      <c r="M16" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="U16" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="V16" s="244" t="inlineStr">
+        <is>
+          <t>5А,6А,8Ә
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="W16" s="244" t="inlineStr">
+        <is>
+          <t>6Б
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AA16" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AD16" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AF16" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AH16" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AI16" s="244" t="inlineStr">
+        <is>
+          <t>6Б
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AJ16" s="244" t="inlineStr">
+        <is>
+          <t>5А,6А
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AL16" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AM16" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Жантимиров</t>
+        </is>
+      </c>
+      <c r="AN16" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Жантимиров</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="248" t="inlineStr">
+        <is>
+          <t>Кабинет физики (№16)</t>
+        </is>
+      </c>
+      <c r="D17" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Русина</t>
+        </is>
+      </c>
+      <c r="E17" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+Русина</t>
+        </is>
+      </c>
+      <c r="F17" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Русина</t>
+        </is>
+      </c>
+      <c r="G17" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Русина</t>
+        </is>
+      </c>
+      <c r="J17" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Русина</t>
+        </is>
+      </c>
+      <c r="K17" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Власова</t>
+        </is>
+      </c>
+      <c r="L17" s="244" t="inlineStr">
         <is>
           <t>8Ә
-Балташева</t>
-        </is>
-      </c>
-      <c r="G9" s="244" t="inlineStr">
+Власова</t>
+        </is>
+      </c>
+      <c r="M17" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Власова</t>
+        </is>
+      </c>
+      <c r="T17" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+Русина</t>
+        </is>
+      </c>
+      <c r="U17" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Русина</t>
+        </is>
+      </c>
+      <c r="W17" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Русина</t>
+        </is>
+      </c>
+      <c r="Z17" s="244" t="inlineStr">
+        <is>
+          <t>5А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="AA17" s="244" t="inlineStr">
+        <is>
+          <t>6А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="AB17" s="244" t="inlineStr">
+        <is>
+          <t>11А
+Ізбасты</t>
+        </is>
+      </c>
+      <c r="AC17" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Русина</t>
+        </is>
+      </c>
+      <c r="AI17" s="244" t="inlineStr">
+        <is>
+          <t>2А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="AJ17" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Русина</t>
+        </is>
+      </c>
+      <c r="AK17" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+Русина</t>
+        </is>
+      </c>
+      <c r="AL17" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Русина</t>
+        </is>
+      </c>
+      <c r="AM17" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Русина</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="248" t="inlineStr">
+        <is>
+          <t>Кабинет химии (№17)</t>
+        </is>
+      </c>
+      <c r="B18" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Бабич</t>
+        </is>
+      </c>
+      <c r="C18" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Бабич</t>
+        </is>
+      </c>
+      <c r="D18" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Бабич</t>
+        </is>
+      </c>
+      <c r="E18" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Бабич</t>
+        </is>
+      </c>
+      <c r="F18" s="244" t="inlineStr">
         <is>
           <t>11А
 Балташева</t>
         </is>
       </c>
-      <c r="J9" s="244" t="inlineStr">
+      <c r="G18" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Красноперова</t>
+        </is>
+      </c>
+      <c r="J18" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Красноперова</t>
+        </is>
+      </c>
+      <c r="K18" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Бабич</t>
+        </is>
+      </c>
+      <c r="L18" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Бабич</t>
+        </is>
+      </c>
+      <c r="M18" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="N18" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Бабич</t>
+        </is>
+      </c>
+      <c r="O18" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Красноперова</t>
+        </is>
+      </c>
+      <c r="P18" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Красноперова</t>
+        </is>
+      </c>
+      <c r="R18" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Бабич</t>
+        </is>
+      </c>
+      <c r="S18" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Красноперова</t>
+        </is>
+      </c>
+      <c r="T18" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="U18" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Бабич</t>
+        </is>
+      </c>
+      <c r="V18" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Бабич</t>
+        </is>
+      </c>
+      <c r="W18" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Красноперова</t>
+        </is>
+      </c>
+      <c r="Z18" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Бабич</t>
+        </is>
+      </c>
+      <c r="AA18" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Бабич</t>
+        </is>
+      </c>
+      <c r="AB18" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Алекпарова</t>
+        </is>
+      </c>
+      <c r="AC18" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Бабич</t>
+        </is>
+      </c>
+      <c r="AD18" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Бабич</t>
+        </is>
+      </c>
+      <c r="AE18" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Красноперова</t>
+        </is>
+      </c>
+      <c r="AF18" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Красноперова</t>
+        </is>
+      </c>
+      <c r="AH18" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Бабич</t>
+        </is>
+      </c>
+      <c r="AI18" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Бабич</t>
+        </is>
+      </c>
+      <c r="AJ18" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Бабич</t>
+        </is>
+      </c>
+      <c r="AK18" s="244" t="inlineStr">
+        <is>
+          <t>8Б
+Бабич</t>
+        </is>
+      </c>
+      <c r="AL18" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Красноперова</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="248" t="inlineStr">
+        <is>
+          <t>Малый зал</t>
+        </is>
+      </c>
+      <c r="B19" s="244" t="inlineStr">
+        <is>
+          <t>11А
+Кашиков</t>
+        </is>
+      </c>
+      <c r="C19" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Кашиков</t>
+        </is>
+      </c>
+      <c r="D19" s="244" t="inlineStr">
+        <is>
+          <t>2А,4А
+Кашиков</t>
+        </is>
+      </c>
+      <c r="E19" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Чифин</t>
+        </is>
+      </c>
+      <c r="F19" s="244" t="inlineStr">
+        <is>
+          <t>5А,6А,8Ә
+Кашиков</t>
+        </is>
+      </c>
+      <c r="G19" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Чифин</t>
+        </is>
+      </c>
+      <c r="K19" s="244" t="inlineStr">
+        <is>
+          <t>5Б
+Чифин</t>
+        </is>
+      </c>
+      <c r="N19" s="244" t="inlineStr">
         <is>
           <t>11Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="K9" s="244" t="inlineStr">
-        <is>
-          <t>6А
-Асаева</t>
-        </is>
-      </c>
-      <c r="L9" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="N9" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="R9" s="244" t="inlineStr">
-        <is>
-          <t>6А
-Асаева</t>
-        </is>
-      </c>
-      <c r="S9" s="244" t="inlineStr">
+Мельников</t>
+        </is>
+      </c>
+      <c r="O19" s="244" t="inlineStr">
+        <is>
+          <t>5А,6А,8Ә
+Кашиков</t>
+        </is>
+      </c>
+      <c r="S19" s="244" t="inlineStr">
+        <is>
+          <t>2А,4А
+Кашиков</t>
+        </is>
+      </c>
+      <c r="T19" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Кашиков</t>
+        </is>
+      </c>
+      <c r="V19" s="244" t="inlineStr">
         <is>
           <t>11Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="T9" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="U9" s="244" t="inlineStr">
+Мельников</t>
+        </is>
+      </c>
+      <c r="AD19" s="244" t="inlineStr">
+        <is>
+          <t>11Б
+Мельников</t>
+        </is>
+      </c>
+      <c r="AE19" s="244" t="inlineStr">
         <is>
           <t>5Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="V9" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="W9" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="Z9" s="244" t="inlineStr">
-        <is>
-          <t>6А
-Асаева</t>
-        </is>
-      </c>
-      <c r="AB9" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="AC9" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AD9" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="AE9" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="AH9" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AI9" s="244" t="inlineStr">
-        <is>
-          <t>6А
-Асаева</t>
-        </is>
-      </c>
-      <c r="AJ9" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AK9" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="AL9" s="244" t="inlineStr">
-        <is>
-          <t>6Б
-Алекпарова</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="248" t="inlineStr">
-        <is>
-          <t>Кабинет казахского языка и литературы (№23)</t>
-        </is>
-      </c>
-      <c r="B10" s="244" t="inlineStr">
+Чифин</t>
+        </is>
+      </c>
+      <c r="AF19" s="244" t="inlineStr">
+        <is>
+          <t>11А
+Кашиков</t>
+        </is>
+      </c>
+      <c r="AI19" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Кашиков</t>
+        </is>
+      </c>
+      <c r="AK19" s="244" t="inlineStr">
+        <is>
+          <t>2А,4А
+Кашиков</t>
+        </is>
+      </c>
+      <c r="AL19" s="244" t="inlineStr">
+        <is>
+          <t>5А,6А,8Ә
+Кашиков</t>
+        </is>
+      </c>
+      <c r="AM19" s="244" t="inlineStr">
+        <is>
+          <t>11А
+Кашиков</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="248" t="inlineStr">
+        <is>
+          <t>Начальный класс 1А (№22)</t>
+        </is>
+      </c>
+      <c r="B20" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="D20" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="E20" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="J20" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="L20" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="R20" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="S20" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="Z20" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="AB20" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="AH20" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="AJ20" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+      <c r="AK20" s="244" t="inlineStr">
+        <is>
+          <t>1А
+Жекеева</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="A21" s="248" t="inlineStr">
+        <is>
+          <t>Начальный класс 1Б (№8)</t>
+        </is>
+      </c>
+      <c r="B21" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="C21" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Власова</t>
+        </is>
+      </c>
+      <c r="D21" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="J21" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="K21" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="L21" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="R21" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="T21" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="U21" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="Z21" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="AA21" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="AB21" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Власова</t>
+        </is>
+      </c>
+      <c r="AC21" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="AH21" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+      <c r="AJ21" s="244" t="inlineStr">
+        <is>
+          <t>1Б
+Ажикенова</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="248" t="inlineStr">
+        <is>
+          <t>Начальный класс 2А/4А (№42)</t>
+        </is>
+      </c>
+      <c r="B22" s="244" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="C22" s="244" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="E22" s="244" t="inlineStr">
         <is>
           <t>2А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="C10" s="244" t="inlineStr">
-        <is>
-          <t>8Ә
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="D10" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="E10" s="244" t="inlineStr">
-        <is>
-          <t>6А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="F10" s="244" t="inlineStr">
-        <is>
-          <t>6Б
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="J10" s="244" t="inlineStr">
-        <is>
-          <t>8Ә
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="K10" s="244" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="L10" s="244" t="inlineStr">
-        <is>
-          <t>6А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="M10" s="244" t="inlineStr">
+Актаева</t>
+        </is>
+      </c>
+      <c r="F22" s="244" t="inlineStr">
         <is>
           <t>4А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="N10" s="244" t="inlineStr">
-        <is>
-          <t>5А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="O10" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="R10" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="S10" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="T10" s="244" t="inlineStr">
-        <is>
-          <t>5А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="U10" s="244" t="inlineStr">
-        <is>
-          <t>6Б
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="W10" s="244" t="inlineStr">
-        <is>
-          <t>11А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="Z10" s="244" t="inlineStr">
-        <is>
-          <t>2А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="AA10" s="244" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="AB10" s="244" t="inlineStr">
-        <is>
-          <t>8Ә
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="AC10" s="244" t="inlineStr">
-        <is>
-          <t>5А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="AD10" s="244" t="inlineStr">
-        <is>
-          <t>6А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="AE10" s="244" t="inlineStr">
-        <is>
-          <t>6Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AF10" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AH10" s="244" t="inlineStr">
+Актаева</t>
+        </is>
+      </c>
+      <c r="J22" s="244" t="inlineStr">
         <is>
           <t>4А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="AI10" s="244" t="inlineStr">
-        <is>
-          <t>8Ә
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AK10" s="244" t="inlineStr">
-        <is>
-          <t>11А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="AL10" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Балгабаева</t>
-        </is>
-      </c>
-      <c r="AM10" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Балгабаева</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="248" t="inlineStr">
-        <is>
-          <t>Кабинет математики (№25)</t>
-        </is>
-      </c>
-      <c r="B11" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-Пащенко</t>
-        </is>
-      </c>
-      <c r="C11" s="244" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Пащенко</t>
-        </is>
-      </c>
-      <c r="E11" s="244" t="inlineStr">
-        <is>
-          <t>6Б
-Мельникова</t>
-        </is>
-      </c>
-      <c r="F11" s="244" t="inlineStr">
+Актаева</t>
+        </is>
+      </c>
+      <c r="K22" s="244" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="M22" s="244" t="inlineStr">
         <is>
           <t>2А
 Жекеева</t>
         </is>
       </c>
-      <c r="K11" s="244" t="inlineStr">
+      <c r="R22" s="244" t="inlineStr">
         <is>
           <t>2А
+Актаева</t>
+        </is>
+      </c>
+      <c r="T22" s="244" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="U22" s="244" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="V22" s="244" t="inlineStr">
+        <is>
+          <t>4А
 Жекеева</t>
         </is>
       </c>
-      <c r="L11" s="244" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Пащенко</t>
-        </is>
-      </c>
-      <c r="M11" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-Пащенко</t>
-        </is>
-      </c>
-      <c r="N11" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Пащенко</t>
-        </is>
-      </c>
-      <c r="R11" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-Пащенко</t>
-        </is>
-      </c>
-      <c r="S11" s="244" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Пащенко</t>
-        </is>
-      </c>
-      <c r="T11" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Пащенко</t>
-        </is>
-      </c>
-      <c r="U11" s="244" t="inlineStr">
-        <is>
-          <t>5А
-Сапаргалиева</t>
-        </is>
-      </c>
-      <c r="V11" s="244" t="inlineStr">
-        <is>
-          <t>11А
-Сапаргалиева</t>
-        </is>
-      </c>
-      <c r="W11" s="244" t="inlineStr">
-        <is>
-          <t>6А
-Сапаргалиева</t>
-        </is>
-      </c>
-      <c r="X11" s="244" t="inlineStr">
-        <is>
-          <t>8Ә
-Сапаргалиева</t>
-        </is>
-      </c>
-      <c r="AA11" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-Пащенко</t>
-        </is>
-      </c>
-      <c r="AB11" s="244" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Пащенко</t>
-        </is>
-      </c>
-      <c r="AC11" s="244" t="inlineStr">
-        <is>
-          <t>6А
-Сапаргалиева</t>
-        </is>
-      </c>
-      <c r="AD11" s="244" t="inlineStr">
-        <is>
-          <t>5А
-Сапаргалиева</t>
-        </is>
-      </c>
-      <c r="AE11" s="244" t="inlineStr">
-        <is>
-          <t>11А
-Сапаргалиева</t>
-        </is>
-      </c>
-      <c r="AF11" s="244" t="inlineStr">
-        <is>
-          <t>8Ә
-Сапаргалиева</t>
-        </is>
-      </c>
-      <c r="AH11" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-Пащенко</t>
-        </is>
-      </c>
-      <c r="AI11" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-Пащенко</t>
-        </is>
-      </c>
-      <c r="AJ11" s="244" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Пащенко</t>
-        </is>
-      </c>
-      <c r="AK11" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Мельникова</t>
-        </is>
-      </c>
-      <c r="AL11" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Мельникова</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="248" t="inlineStr">
-        <is>
-          <t>Кабинет мультимедийный (№18)</t>
-        </is>
-      </c>
-      <c r="B12" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="C12" s="244" t="inlineStr">
-        <is>
-          <t>11А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="D12" s="244" t="inlineStr">
-        <is>
-          <t>5А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="F12" s="244" t="inlineStr">
-        <is>
-          <t>6Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="J12" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="K12" s="244" t="inlineStr">
-        <is>
-          <t>6Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="L12" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="M12" s="244" t="inlineStr">
-        <is>
-          <t>5А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="N12" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="O12" s="244" t="inlineStr">
-        <is>
-          <t>11А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="R12" s="244" t="inlineStr">
-        <is>
-          <t>5А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="S12" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="T12" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="U12" s="244" t="inlineStr">
-        <is>
-          <t>6Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="V12" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="Z12" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="AA12" s="244" t="inlineStr">
-        <is>
-          <t>6Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="AC12" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="AD12" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Ильясова</t>
-        </is>
-      </c>
-      <c r="AE12" s="244" t="inlineStr">
-        <is>
-          <t>5А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="AH12" s="244" t="inlineStr">
-        <is>
-          <t>5А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="AI12" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="AJ12" s="244" t="inlineStr">
-        <is>
-          <t>11А
-Ильясова</t>
-        </is>
-      </c>
-      <c r="AK12" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Ильясова</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="248" t="inlineStr">
-        <is>
-          <t>Кабинет робототехники (№15)</t>
-        </is>
-      </c>
-      <c r="B13" s="244" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Иващенко</t>
-        </is>
-      </c>
-      <c r="C13" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Иващенко</t>
-        </is>
-      </c>
-      <c r="E13" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Бучкова</t>
-        </is>
-      </c>
-      <c r="G13" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Бучкова</t>
-        </is>
-      </c>
-      <c r="J13" s="244" t="inlineStr">
-        <is>
-          <t>11А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="K13" s="244" t="inlineStr">
-        <is>
-          <t>8Ә
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="L13" s="244" t="inlineStr">
-        <is>
-          <t>5А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="M13" s="244" t="inlineStr">
-        <is>
-          <t>6А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="N13" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Бучкова</t>
-        </is>
-      </c>
-      <c r="O13" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Бучкова</t>
-        </is>
-      </c>
-      <c r="R13" s="244" t="inlineStr">
-        <is>
-          <t>11А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="S13" s="244" t="inlineStr">
-        <is>
-          <t>5А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="T13" s="244" t="inlineStr">
-        <is>
-          <t>6А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="U13" s="244" t="inlineStr">
-        <is>
-          <t>8Ә
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="V13" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Бучкова</t>
-        </is>
-      </c>
-      <c r="W13" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Бучкова</t>
-        </is>
-      </c>
-      <c r="Z13" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AA13" s="244" t="inlineStr">
-        <is>
-          <t>8Ә
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AB13" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="AC13" s="244" t="inlineStr">
-        <is>
-          <t>11А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="AD13" s="244" t="inlineStr">
-        <is>
-          <t>8Ә
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="AE13" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Бучкова</t>
-        </is>
-      </c>
-      <c r="AH13" s="244" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Иващенко</t>
-        </is>
-      </c>
-      <c r="AI13" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Иващенко</t>
-        </is>
-      </c>
-      <c r="AK13" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Бучкова</t>
-        </is>
-      </c>
-      <c r="AL13" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Бучкова</t>
-        </is>
-      </c>
-      <c r="AM13" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Бучкова</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="248" t="inlineStr">
-        <is>
-          <t>Кабинет русского языка (№20)</t>
-        </is>
-      </c>
-      <c r="B14" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="C14" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="D14" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="E14" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="F14" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="L14" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="M14" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="N14" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="P14" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="R14" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="S14" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="T14" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="U14" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="V14" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="W14" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="Z14" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="AA14" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="AB14" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="AC14" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="AD14" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="AH14" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="AI14" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="AJ14" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Дмитриев</t>
-        </is>
-      </c>
-      <c r="AK14" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Дмитриев</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="248" t="inlineStr">
-        <is>
-          <t>Кабинет технологии (девочки) (№29)</t>
-        </is>
-      </c>
-      <c r="C15" s="244" t="inlineStr">
+      <c r="Z22" s="244" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="AA22" s="244" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="AC22" s="244" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="AD22" s="244" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="AH22" s="244" t="inlineStr">
         <is>
           <t>2А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="D15" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="E15" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="F15" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="G15" s="244" t="inlineStr">
-        <is>
-          <t>6Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="J15" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="K15" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="L15" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="N15" s="244" t="inlineStr">
-        <is>
-          <t>8Ә
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="O15" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="S15" s="244" t="inlineStr">
+Актаева</t>
+        </is>
+      </c>
+      <c r="AI22" s="244" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="AJ22" s="244" t="inlineStr">
+        <is>
+          <t>2А,4А
+Актаева</t>
+        </is>
+      </c>
+      <c r="AL22" s="244" t="inlineStr">
+        <is>
+          <t>4А
+Актаева</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="248" t="inlineStr">
+        <is>
+          <t>Начальный класс 2Б (№6)</t>
+        </is>
+      </c>
+      <c r="B23" s="244" t="inlineStr">
         <is>
           <t>2Б
-Жукова</t>
-        </is>
-      </c>
-      <c r="T15" s="244" t="inlineStr">
-        <is>
-          <t>2А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="U15" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Жукова</t>
-        </is>
-      </c>
-      <c r="V15" s="244" t="inlineStr">
+Квашнина</t>
+        </is>
+      </c>
+      <c r="C23" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="D23" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="J23" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="K23" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="L23" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="M23" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="R23" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="T23" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="Z23" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="AA23" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="AB23" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="AC23" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="AH23" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="AI23" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Квашнина</t>
+        </is>
+      </c>
+      <c r="AL23" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Асаева</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="248" t="inlineStr">
+        <is>
+          <t>Начальный класс 3А (№7)</t>
+        </is>
+      </c>
+      <c r="B24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="C24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="D24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Власова</t>
+        </is>
+      </c>
+      <c r="E24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="J24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="K24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="L24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="R24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="S24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="U24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="V24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Акауова</t>
+        </is>
+      </c>
+      <c r="Z24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="AA24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="AB24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="AC24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Власова</t>
+        </is>
+      </c>
+      <c r="AD24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="AH24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="AI24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Темерканова</t>
+        </is>
+      </c>
+      <c r="AK24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Акауова</t>
+        </is>
+      </c>
+      <c r="AM24" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Власова</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="248" t="inlineStr">
+        <is>
+          <t>Начальный класс 4Б (№9)</t>
+        </is>
+      </c>
+      <c r="B25" s="244" t="inlineStr">
         <is>
           <t>4Б
 Радионова</t>
         </is>
       </c>
-      <c r="W15" s="244" t="inlineStr">
-        <is>
-          <t>6Б
-Жукова</t>
-        </is>
-      </c>
-      <c r="AA15" s="244" t="inlineStr">
-        <is>
-          <t>2А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="AB15" s="244" t="inlineStr">
-        <is>
-          <t>2А,4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="AC15" s="244" t="inlineStr">
-        <is>
-          <t>2А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="AD15" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Жукова</t>
-        </is>
-      </c>
-      <c r="AF15" s="244" t="inlineStr">
+      <c r="C25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="E25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="F25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="J25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="K25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="L25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="M25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="N25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="R25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="S25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="U25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Асаева</t>
+        </is>
+      </c>
+      <c r="W25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Акауова</t>
+        </is>
+      </c>
+      <c r="Z25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="AA25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="AB25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="AC25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Акауова</t>
+        </is>
+      </c>
+      <c r="AD25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="AH25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="AI25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Радионова</t>
+        </is>
+      </c>
+      <c r="AJ25" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Асаева</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="248" t="inlineStr">
+        <is>
+          <t>Спортивный зал (№01)</t>
+        </is>
+      </c>
+      <c r="B26" s="244" t="inlineStr">
+        <is>
+          <t>10А
+Мельников</t>
+        </is>
+      </c>
+      <c r="C26" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Мельников</t>
+        </is>
+      </c>
+      <c r="D26" s="244" t="inlineStr">
+        <is>
+          <t>4Б
+Чифин</t>
+        </is>
+      </c>
+      <c r="E26" s="244" t="inlineStr">
+        <is>
+          <t>2Б
+Ольков</t>
+        </is>
+      </c>
+      <c r="F26" s="244" t="inlineStr">
+        <is>
+          <t>3А
+Чифин</t>
+        </is>
+      </c>
+      <c r="G26" s="244" t="inlineStr">
+        <is>
+          <t>7А
+Ольков</t>
+        </is>
+      </c>
+      <c r="H26" s="244" t="inlineStr">
         <is>
           <t>8А
-Жукова</t>
-        </is>
-      </c>
-      <c r="AI15" s="244" t="inlineStr">
+Ольков</t>
+        </is>
+      </c>
+      <c r="K26" s="244" t="inlineStr">
+        <is>
+          <t>9Б
+Мельников</t>
+        </is>
+      </c>
+      <c r="M26" s="244" t="inlineStr">
         <is>
           <t>6Б,6В
-Жукова</t>
-        </is>
-      </c>
-      <c r="AJ15" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Жукова</t>
-        </is>
-      </c>
-      <c r="AK15" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="AL15" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Жукова</t>
-        </is>
-      </c>
-      <c r="AM15" s="244" t="inlineStr">
+Ольков</t>
+        </is>
+      </c>
+      <c r="O26" s="244" t="inlineStr">
+        <is>
+          <t>8А
+Ольков</t>
+        </is>
+      </c>
+      <c r="P26" s="244" t="inlineStr">
         <is>
           <t>8Б
-Жукова</t>
-        </is>
-      </c>
-      <c r="AN15" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Жукова</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="248" t="inlineStr">
-        <is>
-          <t>Кабинет технологии (мальчики) (№39)</t>
-        </is>
-      </c>
-      <c r="D16" s="244" t="inlineStr">
+Ольков</t>
+        </is>
+      </c>
+      <c r="R26" s="244" t="inlineStr">
         <is>
           <t>6Б,6В
-Темерканова</t>
-        </is>
-      </c>
-      <c r="M16" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="N16" s="244" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Темерканова</t>
-        </is>
-      </c>
-      <c r="T16" s="244" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Темерканова</t>
-        </is>
-      </c>
-      <c r="U16" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="V16" s="244" t="inlineStr">
-        <is>
-          <t>5А,6А,8Ә
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="W16" s="244" t="inlineStr">
-        <is>
-          <t>6Б
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="AA16" s="244" t="inlineStr">
-        <is>
-          <t>1А
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="AC16" s="244" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Темерканова</t>
-        </is>
-      </c>
-      <c r="AD16" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="AF16" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="AI16" s="244" t="inlineStr">
-        <is>
-          <t>6Б
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="AJ16" s="244" t="inlineStr">
-        <is>
-          <t>5А,6А
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="AK16" s="244" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Темерканова</t>
-        </is>
-      </c>
-      <c r="AL16" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="AM16" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Жантимиров</t>
-        </is>
-      </c>
-      <c r="AN16" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Жантимиров</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="248" t="inlineStr">
-        <is>
-          <t>Кабинет физики (№16)</t>
-        </is>
-      </c>
-      <c r="D17" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Русина</t>
-        </is>
-      </c>
-      <c r="E17" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-Русина</t>
-        </is>
-      </c>
-      <c r="F17" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Русина</t>
-        </is>
-      </c>
-      <c r="G17" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Русина</t>
-        </is>
-      </c>
-      <c r="J17" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Русина</t>
-        </is>
-      </c>
-      <c r="K17" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Дюсембаева</t>
-        </is>
-      </c>
-      <c r="L17" s="244" t="inlineStr">
-        <is>
-          <t>8Ә
-Дюсембаева</t>
-        </is>
-      </c>
-      <c r="M17" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Дюсембаева</t>
-        </is>
-      </c>
-      <c r="T17" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-Русина</t>
-        </is>
-      </c>
-      <c r="U17" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Русина</t>
-        </is>
-      </c>
-      <c r="X17" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Русина</t>
-        </is>
-      </c>
-      <c r="Z17" s="244" t="inlineStr">
-        <is>
-          <t>5А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="AA17" s="244" t="inlineStr">
-        <is>
-          <t>6А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="AB17" s="244" t="inlineStr">
-        <is>
-          <t>11А
-Ізбасты</t>
-        </is>
-      </c>
-      <c r="AC17" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Русина</t>
-        </is>
-      </c>
-      <c r="AH17" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Русина</t>
-        </is>
-      </c>
-      <c r="AI17" s="244" t="inlineStr">
-        <is>
-          <t>2А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="AJ17" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Русина</t>
-        </is>
-      </c>
-      <c r="AK17" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-Русина</t>
-        </is>
-      </c>
-      <c r="AL17" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Русина</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="248" t="inlineStr">
-        <is>
-          <t>Кабинет химии (№17)</t>
-        </is>
-      </c>
-      <c r="B18" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Бабич</t>
-        </is>
-      </c>
-      <c r="C18" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Бабич</t>
-        </is>
-      </c>
-      <c r="D18" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Бабич</t>
-        </is>
-      </c>
-      <c r="E18" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Бабич</t>
-        </is>
-      </c>
-      <c r="F18" s="244" t="inlineStr">
-        <is>
-          <t>11А
-Балташева</t>
-        </is>
-      </c>
-      <c r="G18" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Красноперова</t>
-        </is>
-      </c>
-      <c r="J18" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Красноперова</t>
-        </is>
-      </c>
-      <c r="K18" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Бабич</t>
-        </is>
-      </c>
-      <c r="L18" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Бабич</t>
-        </is>
-      </c>
-      <c r="M18" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="N18" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Бабич</t>
-        </is>
-      </c>
-      <c r="O18" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Красноперова</t>
-        </is>
-      </c>
-      <c r="P18" s="244" t="inlineStr">
-        <is>
-          <t>7А
-Красноперова</t>
-        </is>
-      </c>
-      <c r="R18" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Бабич</t>
-        </is>
-      </c>
-      <c r="S18" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Красноперова</t>
-        </is>
-      </c>
-      <c r="T18" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="U18" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Бабич</t>
-        </is>
-      </c>
-      <c r="V18" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Бабич</t>
-        </is>
-      </c>
-      <c r="W18" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Красноперова</t>
-        </is>
-      </c>
-      <c r="Z18" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Бабич</t>
-        </is>
-      </c>
-      <c r="AA18" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Бабич</t>
-        </is>
-      </c>
-      <c r="AB18" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Алекпарова</t>
-        </is>
-      </c>
-      <c r="AC18" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Бабич</t>
-        </is>
-      </c>
-      <c r="AD18" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Бабич</t>
-        </is>
-      </c>
-      <c r="AE18" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Красноперова</t>
-        </is>
-      </c>
-      <c r="AF18" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Красноперова</t>
-        </is>
-      </c>
-      <c r="AH18" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Бабич</t>
-        </is>
-      </c>
-      <c r="AI18" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Бабич</t>
-        </is>
-      </c>
-      <c r="AJ18" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Бабич</t>
-        </is>
-      </c>
-      <c r="AK18" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Бабич</t>
-        </is>
-      </c>
-      <c r="AL18" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Красноперова</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="248" t="inlineStr">
-        <is>
-          <t>Малый зал</t>
-        </is>
-      </c>
-      <c r="B19" s="244" t="inlineStr">
-        <is>
-          <t>11А
-Кашиков</t>
-        </is>
-      </c>
-      <c r="C19" s="244" t="inlineStr">
-        <is>
-          <t>1А
-Кашиков</t>
-        </is>
-      </c>
-      <c r="D19" s="244" t="inlineStr">
-        <is>
-          <t>2А,4А
-Кашиков</t>
-        </is>
-      </c>
-      <c r="E19" s="244" t="inlineStr">
+Ольков</t>
+        </is>
+      </c>
+      <c r="S26" s="244" t="inlineStr">
         <is>
           <t>1Б
 Чифин</t>
         </is>
       </c>
-      <c r="F19" s="244" t="inlineStr">
-        <is>
-          <t>5А,6А,8Ә
-Кашиков</t>
-        </is>
-      </c>
-      <c r="G19" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Чифин</t>
-        </is>
-      </c>
-      <c r="K19" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Чифин</t>
-        </is>
-      </c>
-      <c r="N19" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-Мельников</t>
-        </is>
-      </c>
-      <c r="O19" s="244" t="inlineStr">
-        <is>
-          <t>5А,6А,8Ә
-Кашиков</t>
-        </is>
-      </c>
-      <c r="S19" s="244" t="inlineStr">
-        <is>
-          <t>2А,4А
-Кашиков</t>
-        </is>
-      </c>
-      <c r="T19" s="244" t="inlineStr">
-        <is>
-          <t>1А
-Кашиков</t>
-        </is>
-      </c>
-      <c r="V19" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-Мельников</t>
-        </is>
-      </c>
-      <c r="AD19" s="244" t="inlineStr">
-        <is>
-          <t>11Б
-Мельников</t>
-        </is>
-      </c>
-      <c r="AE19" s="244" t="inlineStr">
-        <is>
-          <t>5Б
-Чифин</t>
-        </is>
-      </c>
-      <c r="AF19" s="244" t="inlineStr">
-        <is>
-          <t>11А
-Кашиков</t>
-        </is>
-      </c>
-      <c r="AI19" s="244" t="inlineStr">
-        <is>
-          <t>1А
-Кашиков</t>
-        </is>
-      </c>
-      <c r="AK19" s="244" t="inlineStr">
-        <is>
-          <t>2А,4А
-Кашиков</t>
-        </is>
-      </c>
-      <c r="AL19" s="244" t="inlineStr">
-        <is>
-          <t>5А,6А,8Ә
-Кашиков</t>
-        </is>
-      </c>
-      <c r="AM19" s="244" t="inlineStr">
-        <is>
-          <t>11А
-Кашиков</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="248" t="inlineStr">
-        <is>
-          <t>Начальный класс 1А (№22)</t>
-        </is>
-      </c>
-      <c r="B20" s="244" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="D20" s="244" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="E20" s="244" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="J20" s="244" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="L20" s="244" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="R20" s="244" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="S20" s="244" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="Z20" s="244" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="AB20" s="244" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="AH20" s="244" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="AJ20" s="244" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="AK20" s="244" t="inlineStr">
-        <is>
-          <t>1А
-Жекеева</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="248" t="inlineStr">
-        <is>
-          <t>Начальный класс 1Б (№8)</t>
-        </is>
-      </c>
-      <c r="B21" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="C21" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Дюсембаева</t>
-        </is>
-      </c>
-      <c r="D21" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="J21" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="K21" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="L21" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="R21" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="T21" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="U21" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="Z21" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="AA21" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="AB21" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Дюсембаева</t>
-        </is>
-      </c>
-      <c r="AC21" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="AH21" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-      <c r="AJ21" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Ажикенова</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="248" t="inlineStr">
-        <is>
-          <t>Начальный класс 2А/4А (№42)</t>
-        </is>
-      </c>
-      <c r="B22" s="244" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="C22" s="244" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="E22" s="244" t="inlineStr">
-        <is>
-          <t>2А
-Актаева</t>
-        </is>
-      </c>
-      <c r="F22" s="244" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="J22" s="244" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="K22" s="244" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="M22" s="244" t="inlineStr">
-        <is>
-          <t>2А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="R22" s="244" t="inlineStr">
-        <is>
-          <t>2А
-Актаева</t>
-        </is>
-      </c>
-      <c r="T22" s="244" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="U22" s="244" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="V22" s="244" t="inlineStr">
-        <is>
-          <t>4А
-Жекеева</t>
-        </is>
-      </c>
-      <c r="Z22" s="244" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="AA22" s="244" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="AC22" s="244" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="AD22" s="244" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="AH22" s="244" t="inlineStr">
-        <is>
-          <t>2А
-Актаева</t>
-        </is>
-      </c>
-      <c r="AI22" s="244" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="AJ22" s="244" t="inlineStr">
-        <is>
-          <t>2А,4А
-Актаева</t>
-        </is>
-      </c>
-      <c r="AL22" s="244" t="inlineStr">
-        <is>
-          <t>4А
-Актаева</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="248" t="inlineStr">
-        <is>
-          <t>Начальный класс 2Б (№6)</t>
-        </is>
-      </c>
-      <c r="B23" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="C23" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="D23" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="J23" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="K23" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="L23" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="M23" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="R23" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="T23" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="Z23" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="AA23" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="AB23" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="AC23" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="AH23" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="AI23" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Квашнина</t>
-        </is>
-      </c>
-      <c r="AL23" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Асаева</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="248" t="inlineStr">
-        <is>
-          <t>Начальный класс 3А (№7)</t>
-        </is>
-      </c>
-      <c r="B24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="C24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="D24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Дюсембаева</t>
-        </is>
-      </c>
-      <c r="E24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="J24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="K24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="L24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="R24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="S24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="U24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="V24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Акауова</t>
-        </is>
-      </c>
-      <c r="Z24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="AA24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="AB24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="AC24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Дюсембаева</t>
-        </is>
-      </c>
-      <c r="AD24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="AH24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="AI24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Темерканова</t>
-        </is>
-      </c>
-      <c r="AK24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Акауова</t>
-        </is>
-      </c>
-      <c r="AM24" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Дюсембаева</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="248" t="inlineStr">
-        <is>
-          <t>Начальный класс 4Б (№9)</t>
-        </is>
-      </c>
-      <c r="B25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="C25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="E25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="F25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="J25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="K25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="L25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="M25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="N25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="R25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="S25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="U25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Асаева</t>
-        </is>
-      </c>
-      <c r="W25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Акауова</t>
-        </is>
-      </c>
-      <c r="Z25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="AA25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="AB25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="AC25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Акауова</t>
-        </is>
-      </c>
-      <c r="AD25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="AH25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="AI25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Радионова</t>
-        </is>
-      </c>
-      <c r="AJ25" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Асаева</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="248" t="inlineStr">
-        <is>
-          <t>Спортивный зал (№01)</t>
-        </is>
-      </c>
-      <c r="B26" s="244" t="inlineStr">
-        <is>
-          <t>10А
-Мельников</t>
-        </is>
-      </c>
-      <c r="C26" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Мельников</t>
-        </is>
-      </c>
-      <c r="D26" s="244" t="inlineStr">
+      <c r="T26" s="244" t="inlineStr">
         <is>
           <t>4Б
 Чифин</t>
         </is>
       </c>
-      <c r="E26" s="244" t="inlineStr">
-        <is>
-          <t>2Б
-Ольков</t>
-        </is>
-      </c>
-      <c r="F26" s="244" t="inlineStr">
-        <is>
-          <t>3А
-Чифин</t>
-        </is>
-      </c>
-      <c r="G26" s="244" t="inlineStr">
+      <c r="U26" s="244" t="inlineStr">
         <is>
           <t>7А
 Ольков</t>
-        </is>
-      </c>
-      <c r="H26" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Ольков</t>
-        </is>
-      </c>
-      <c r="K26" s="244" t="inlineStr">
-        <is>
-          <t>9Б
-Мельников</t>
-        </is>
-      </c>
-      <c r="M26" s="244" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Ольков</t>
-        </is>
-      </c>
-      <c r="O26" s="244" t="inlineStr">
-        <is>
-          <t>8А
-Ольков</t>
-        </is>
-      </c>
-      <c r="P26" s="244" t="inlineStr">
-        <is>
-          <t>8Б
-Ольков</t>
-        </is>
-      </c>
-      <c r="R26" s="244" t="inlineStr">
-        <is>
-          <t>6Б,6В
-Ольков</t>
-        </is>
-      </c>
-      <c r="S26" s="244" t="inlineStr">
-        <is>
-          <t>1Б
-Чифин</t>
-        </is>
-      </c>
-      <c r="T26" s="244" t="inlineStr">
-        <is>
-          <t>4Б
-Чифин</t>
         </is>
       </c>
       <c r="V26" s="244" t="inlineStr">
@@ -18742,7 +18769,7 @@
     <row r="34" ht="28" customHeight="1">
       <c r="A34" s="252" t="inlineStr">
         <is>
-          <t>1 урок 10:30–11:15, 2 урок 11:25–12:10, 3 урок 12:20–13:05 (сдвинуто относительно школьных звонков)</t>
+          <t>Пн–Ср: 1 урок 10:30–11:15, 2 урок 11:25–12:10, 3 урок 12:20–13:05. Чт: 10:05–10:50, 11:05–11:50 (по звонкам 3–4 уроков школы, чтобы Жукова успевала к 5 уроку в 5Б)  Свап Ср и Чт: Жукова перенесена со среды на четверг (10:05–11:50), Дукач с четверга на среду (10:30–13:05).</t>
         </is>
       </c>
     </row>
@@ -18971,12 +18998,12 @@
       </c>
       <c r="E41" s="251" t="inlineStr">
         <is>
-          <t>Изобразительное искусство</t>
+          <t>Развитие речи и коммуникации</t>
         </is>
       </c>
       <c r="F41" s="251" t="inlineStr">
         <is>
-          <t>Жукова Ирина Михайловна</t>
+          <t>Дукач Татьяна Анатольевна</t>
         </is>
       </c>
       <c r="G41" s="251" t="inlineStr"/>
@@ -19004,12 +19031,12 @@
       </c>
       <c r="E42" s="251" t="inlineStr">
         <is>
-          <t>Хозяйственный труд</t>
+          <t>Счет</t>
         </is>
       </c>
       <c r="F42" s="251" t="inlineStr">
         <is>
-          <t>Жукова Ирина Михайловна</t>
+          <t>Дукач Татьяна Анатольевна</t>
         </is>
       </c>
       <c r="G42" s="251" t="inlineStr"/>
@@ -19017,27 +19044,27 @@
     <row r="43">
       <c r="A43" s="251" t="inlineStr">
         <is>
-          <t>Чт</t>
+          <t>Ср</t>
         </is>
       </c>
       <c r="B43" s="251" t="inlineStr">
         <is>
-          <t>3–4</t>
+          <t>5–6</t>
         </is>
       </c>
       <c r="C43" s="251" t="inlineStr">
         <is>
-          <t>3-й 10:05–10:50; 4-й 11:05–11:50</t>
+          <t>5-й 11:55–12:40; 6-й 12:45–13:30</t>
         </is>
       </c>
       <c r="D43" s="251" t="inlineStr">
         <is>
-          <t>10:30–11:15</t>
+          <t>12:20–13:05</t>
         </is>
       </c>
       <c r="E43" s="251" t="inlineStr">
         <is>
-          <t>Развитие речи и коммуникации</t>
+          <t>Человек и мир</t>
         </is>
       </c>
       <c r="F43" s="251" t="inlineStr">
@@ -19055,27 +19082,27 @@
       </c>
       <c r="B44" s="251" t="inlineStr">
         <is>
-          <t>4–5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C44" s="251" t="inlineStr">
         <is>
-          <t>4-й 11:05–11:50; 5-й 11:55–12:40</t>
+          <t>3-й 10:05–10:50</t>
         </is>
       </c>
       <c r="D44" s="251" t="inlineStr">
         <is>
-          <t>11:25–12:10</t>
+          <t>10:05–10:50</t>
         </is>
       </c>
       <c r="E44" s="251" t="inlineStr">
         <is>
-          <t>Счет</t>
+          <t>Изобразительное искусство</t>
         </is>
       </c>
       <c r="F44" s="251" t="inlineStr">
         <is>
-          <t>Дукач Татьяна Анатольевна</t>
+          <t>Жукова Ирина Михайловна</t>
         </is>
       </c>
       <c r="G44" s="251" t="inlineStr"/>
@@ -19088,27 +19115,27 @@
       </c>
       <c r="B45" s="251" t="inlineStr">
         <is>
-          <t>5–6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C45" s="251" t="inlineStr">
         <is>
-          <t>5-й 11:55–12:40; 6-й 12:45–13:30</t>
+          <t>4-й 11:05–11:50</t>
         </is>
       </c>
       <c r="D45" s="251" t="inlineStr">
         <is>
-          <t>12:20–13:05</t>
+          <t>11:05–11:50</t>
         </is>
       </c>
       <c r="E45" s="251" t="inlineStr">
         <is>
-          <t>Человек и мир</t>
+          <t>Хозяйственный труд</t>
         </is>
       </c>
       <c r="F45" s="251" t="inlineStr">
         <is>
-          <t>Дукач Татьяна Анатольевна</t>
+          <t>Жукова Ирина Михайловна</t>
         </is>
       </c>
       <c r="G45" s="251" t="inlineStr"/>
